--- a/data/herbicide_records.xlsx
+++ b/data/herbicide_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="377">
   <si>
     <t>Date</t>
   </si>
@@ -754,6 +754,402 @@
   </si>
   <si>
     <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>DG24004</t>
+  </si>
+  <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>DG21001</t>
+  </si>
+  <si>
+    <t>DG24005</t>
+  </si>
+  <si>
+    <t>DG21002</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>DG24006</t>
+  </si>
+  <si>
+    <t>DG21003</t>
+  </si>
+  <si>
+    <t>DG24007</t>
+  </si>
+  <si>
+    <t>DG36004</t>
+  </si>
+  <si>
+    <t>DG24008</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>DG21004</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>2025-11-08</t>
+  </si>
+  <si>
+    <t>DG21005</t>
+  </si>
+  <si>
+    <t>2025-11-09</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-13</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
+  </si>
+  <si>
+    <t>DG21006</t>
+  </si>
+  <si>
+    <t>DG33000</t>
+  </si>
+  <si>
+    <t>2025-11-16</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>2025-11-23</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>DG36003</t>
+  </si>
+  <si>
+    <t>DG25001</t>
+  </si>
+  <si>
+    <t>DG25002</t>
+  </si>
+  <si>
+    <t>DG33002</t>
+  </si>
+  <si>
+    <t>DG33003</t>
+  </si>
+  <si>
+    <t>DG33-39</t>
+  </si>
+  <si>
+    <t>DG33004</t>
+  </si>
+  <si>
+    <t>DG33005</t>
+  </si>
+  <si>
+    <t>DG33006</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>DG33007</t>
+  </si>
+  <si>
+    <t>DG33008</t>
+  </si>
+  <si>
+    <t>DG25003</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>DG25004</t>
+  </si>
+  <si>
+    <t>2025-11-29</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>DG24001</t>
+  </si>
+  <si>
+    <t>DG24002</t>
+  </si>
+  <si>
+    <t>DG24003</t>
+  </si>
+  <si>
+    <t>DG23001</t>
+  </si>
+  <si>
+    <t>DG23002</t>
+  </si>
+  <si>
+    <t>DG19002</t>
+  </si>
+  <si>
+    <t>DG19003</t>
+  </si>
+  <si>
+    <t>DG19004</t>
+  </si>
+  <si>
+    <t>DG18-29</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>DG19005</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2025-12-13</t>
+  </si>
+  <si>
+    <t>2025-12-14</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>DG19006</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>2025-12-21</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>2025-12-23</t>
+  </si>
+  <si>
+    <t>2025-12-24</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>2025-12-26</t>
+  </si>
+  <si>
+    <t>2025-12-27</t>
+  </si>
+  <si>
+    <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>DG31000</t>
+  </si>
+  <si>
+    <t>2026-01-03</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>DG23006</t>
+  </si>
+  <si>
+    <t>DG23005</t>
+  </si>
+  <si>
+    <t>DG23004</t>
+  </si>
+  <si>
+    <t>DG23003</t>
+  </si>
+  <si>
+    <t>DG30008</t>
+  </si>
+  <si>
+    <t>DG30007</t>
+  </si>
+  <si>
+    <t>DG30006</t>
+  </si>
+  <si>
+    <t>DG29-33</t>
+  </si>
+  <si>
+    <t>DG29-39</t>
+  </si>
+  <si>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>DG30001</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>2026-01-18</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>DG30002</t>
+  </si>
+  <si>
+    <t>DG30003</t>
+  </si>
+  <si>
+    <t>DG30004</t>
+  </si>
+  <si>
+    <t>DG30005</t>
+  </si>
+  <si>
+    <t>DG39001</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R269"/>
+  <dimension ref="A1:R457"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11498,21 +11894,33 @@
       <c r="A218" t="s">
         <v>206</v>
       </c>
+      <c r="R218" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>207</v>
       </c>
+      <c r="R219" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>208</v>
       </c>
+      <c r="R220" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>209</v>
       </c>
+      <c r="R221" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -11798,6 +12206,9 @@
       <c r="A227" t="s">
         <v>218</v>
       </c>
+      <c r="R227" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
@@ -11859,11 +12270,17 @@
       <c r="A229" t="s">
         <v>220</v>
       </c>
+      <c r="R229" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>221</v>
       </c>
+      <c r="R230" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
@@ -11925,16 +12342,25 @@
       <c r="A232" t="s">
         <v>223</v>
       </c>
+      <c r="R232" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>224</v>
       </c>
+      <c r="R233" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>225</v>
       </c>
+      <c r="R234" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
@@ -12901,6 +13327,48 @@
       <c r="D252">
         <v>2.99</v>
       </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>6</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0</v>
+      </c>
+      <c r="P252">
+        <v>0</v>
+      </c>
+      <c r="Q252">
+        <v>4</v>
+      </c>
+      <c r="R252" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
@@ -12915,6 +13383,48 @@
       <c r="D253">
         <v>2.99</v>
       </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>0</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>6</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0</v>
+      </c>
+      <c r="P253">
+        <v>0</v>
+      </c>
+      <c r="Q253">
+        <v>3</v>
+      </c>
+      <c r="R253" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
@@ -12929,6 +13439,45 @@
       <c r="D254">
         <v>3.13</v>
       </c>
+      <c r="E254">
+        <v>6</v>
+      </c>
+      <c r="F254">
+        <v>6</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0</v>
+      </c>
+      <c r="Q254">
+        <v>4</v>
+      </c>
+      <c r="R254" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
@@ -12943,11 +13492,53 @@
       <c r="D255">
         <v>3.13</v>
       </c>
+      <c r="E255">
+        <v>6</v>
+      </c>
+      <c r="F255">
+        <v>6</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>0</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>0</v>
+      </c>
+      <c r="P255">
+        <v>0</v>
+      </c>
+      <c r="Q255">
+        <v>3</v>
+      </c>
+      <c r="R255" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>240</v>
       </c>
+      <c r="R256" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
@@ -12962,6 +13553,48 @@
       <c r="D257">
         <v>2.99</v>
       </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>0</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>6</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>0</v>
+      </c>
+      <c r="P257">
+        <v>0</v>
+      </c>
+      <c r="Q257">
+        <v>4</v>
+      </c>
+      <c r="R257" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
@@ -12976,6 +13609,48 @@
       <c r="D258">
         <v>4.63</v>
       </c>
+      <c r="E258">
+        <v>10</v>
+      </c>
+      <c r="F258">
+        <v>10</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>0</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0</v>
+      </c>
+      <c r="Q258">
+        <v>3</v>
+      </c>
+      <c r="R258" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
@@ -12990,6 +13665,48 @@
       <c r="D259">
         <v>3</v>
       </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>0</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>15</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0</v>
+      </c>
+      <c r="Q259">
+        <v>7</v>
+      </c>
+      <c r="R259" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
@@ -13004,6 +13721,48 @@
       <c r="D260">
         <v>2.99</v>
       </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>6</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>4</v>
+      </c>
+      <c r="R260" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
@@ -13018,6 +13777,48 @@
       <c r="D261">
         <v>2.99</v>
       </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>6</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>3</v>
+      </c>
+      <c r="R261" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
@@ -13032,30 +13833,179 @@
       <c r="D262">
         <v>2.99</v>
       </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>6</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>3</v>
+      </c>
+      <c r="R262" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>244</v>
       </c>
+      <c r="B263" t="s">
+        <v>245</v>
+      </c>
+      <c r="C263" t="s">
+        <v>246</v>
+      </c>
+      <c r="D263">
+        <v>3.03</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>6</v>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>6</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>4</v>
+      </c>
+      <c r="R263" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>247</v>
+      </c>
+      <c r="B264" t="s">
+        <v>248</v>
+      </c>
+      <c r="C264" t="s">
+        <v>41</v>
+      </c>
+      <c r="D264">
+        <v>3.03</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>6</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>6</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
+        <v>3</v>
+      </c>
+      <c r="R264" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>56</v>
       </c>
       <c r="B265" t="s">
-        <v>51</v>
+        <v>249</v>
       </c>
       <c r="C265" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="D265">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="E265">
         <v>0</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -13070,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="K265">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -13088,7 +14038,7 @@
         <v>0</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R265" t="s">
         <v>21</v>
@@ -13096,22 +14046,22 @@
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B266" t="s">
-        <v>51</v>
+        <v>250</v>
       </c>
       <c r="C266" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="E266">
         <v>0</v>
       </c>
       <c r="F266">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G266">
         <v>0</v>
@@ -13126,7 +14076,7 @@
         <v>0</v>
       </c>
       <c r="K266">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -13144,7 +14094,7 @@
         <v>0</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R266" t="s">
         <v>21</v>
@@ -13152,22 +14102,55 @@
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="B267" t="s">
-        <v>51</v>
+        <v>254</v>
       </c>
       <c r="C267" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="E267">
         <v>0</v>
       </c>
+      <c r="F267">
+        <v>6</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>6</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>0</v>
+      </c>
+      <c r="N267">
+        <v>0</v>
+      </c>
+      <c r="O267">
+        <v>0</v>
+      </c>
+      <c r="P267">
+        <v>0</v>
+      </c>
       <c r="Q267">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R267" t="s">
         <v>21</v>
@@ -13175,19 +14158,55 @@
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="B268" t="s">
-        <v>51</v>
+        <v>255</v>
       </c>
       <c r="C268" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="E268">
         <v>0</v>
+      </c>
+      <c r="F268">
+        <v>2</v>
+      </c>
+      <c r="G268">
+        <v>0</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>2</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>0</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268">
+        <v>0</v>
+      </c>
+      <c r="P268">
+        <v>0</v>
+      </c>
+      <c r="Q268">
+        <v>2</v>
       </c>
       <c r="R268" t="s">
         <v>21</v>
@@ -13195,33 +14214,6151 @@
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>252</v>
+      </c>
+      <c r="B269" t="s">
+        <v>198</v>
+      </c>
+      <c r="C269" t="s">
+        <v>38</v>
+      </c>
+      <c r="D269">
+        <v>2.99</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>0</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269">
+        <v>150</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+      <c r="L269">
+        <v>0</v>
+      </c>
+      <c r="M269">
+        <v>0</v>
+      </c>
+      <c r="N269">
+        <v>0</v>
+      </c>
+      <c r="O269">
+        <v>0</v>
+      </c>
+      <c r="P269">
+        <v>0</v>
+      </c>
+      <c r="Q269">
+        <v>4</v>
+      </c>
+      <c r="R269" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>252</v>
+      </c>
+      <c r="B270" t="s">
+        <v>200</v>
+      </c>
+      <c r="C270" t="s">
+        <v>38</v>
+      </c>
+      <c r="D270">
+        <v>2.99</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>0</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270">
+        <v>150</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>0</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>0</v>
+      </c>
+      <c r="O270">
+        <v>0</v>
+      </c>
+      <c r="P270">
+        <v>0</v>
+      </c>
+      <c r="Q270">
+        <v>3</v>
+      </c>
+      <c r="R270" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>252</v>
+      </c>
+      <c r="B271" t="s">
+        <v>256</v>
+      </c>
+      <c r="C271" t="s">
+        <v>246</v>
+      </c>
+      <c r="D271">
+        <v>3.03</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>6</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>6</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+      <c r="M271">
+        <v>0</v>
+      </c>
+      <c r="N271">
+        <v>0</v>
+      </c>
+      <c r="O271">
+        <v>0</v>
+      </c>
+      <c r="P271">
+        <v>0</v>
+      </c>
+      <c r="Q271">
+        <v>3</v>
+      </c>
+      <c r="R271" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>252</v>
+      </c>
+      <c r="B272" t="s">
+        <v>19</v>
+      </c>
+      <c r="C272" t="s">
+        <v>20</v>
+      </c>
+      <c r="D272">
+        <v>3.14</v>
+      </c>
+      <c r="E272">
+        <v>6</v>
+      </c>
+      <c r="F272">
+        <v>6</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>0</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>0</v>
+      </c>
+      <c r="O272">
+        <v>0</v>
+      </c>
+      <c r="P272">
+        <v>0</v>
+      </c>
+      <c r="Q272">
+        <v>3</v>
+      </c>
+      <c r="R272" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>252</v>
+      </c>
+      <c r="B273" t="s">
+        <v>257</v>
+      </c>
+      <c r="C273" t="s">
+        <v>38</v>
+      </c>
+      <c r="D273">
+        <v>2.08</v>
+      </c>
+      <c r="E273">
+        <v>6</v>
+      </c>
+      <c r="F273">
+        <v>6</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>0</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+      <c r="M273">
+        <v>0</v>
+      </c>
+      <c r="N273">
+        <v>0</v>
+      </c>
+      <c r="O273">
+        <v>0</v>
+      </c>
+      <c r="P273">
+        <v>0</v>
+      </c>
+      <c r="Q273">
+        <v>3</v>
+      </c>
+      <c r="R273" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>253</v>
+      </c>
+      <c r="B274" t="s">
+        <v>258</v>
+      </c>
+      <c r="C274" t="s">
+        <v>246</v>
+      </c>
+      <c r="D274">
+        <v>3</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>6</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>6</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+      <c r="M274">
+        <v>0</v>
+      </c>
+      <c r="N274">
+        <v>0</v>
+      </c>
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0</v>
+      </c>
+      <c r="Q274">
+        <v>4</v>
+      </c>
+      <c r="R274" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>253</v>
+      </c>
+      <c r="B275" t="s">
+        <v>201</v>
+      </c>
+      <c r="C275" t="s">
+        <v>38</v>
+      </c>
+      <c r="D275">
+        <v>2.99</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>150</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>0</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275">
+        <v>0</v>
+      </c>
+      <c r="P275">
+        <v>0</v>
+      </c>
+      <c r="Q275">
+        <v>3</v>
+      </c>
+      <c r="R275" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>253</v>
+      </c>
+      <c r="B276" t="s">
+        <v>214</v>
+      </c>
+      <c r="C276" t="s">
+        <v>38</v>
+      </c>
+      <c r="D276">
+        <v>2.99</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>150</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>0</v>
+      </c>
+      <c r="O276">
+        <v>0</v>
+      </c>
+      <c r="P276">
+        <v>0</v>
+      </c>
+      <c r="Q276">
+        <v>3</v>
+      </c>
+      <c r="R276" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>259</v>
+      </c>
+      <c r="R277" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>260</v>
+      </c>
+      <c r="B278" t="s">
+        <v>255</v>
+      </c>
+      <c r="C278" t="s">
+        <v>41</v>
+      </c>
+      <c r="D278">
+        <v>3.02</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>6</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>6</v>
+      </c>
+      <c r="L278">
+        <v>0</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
+      </c>
+      <c r="N278">
+        <v>0</v>
+      </c>
+      <c r="O278">
+        <v>0</v>
+      </c>
+      <c r="P278">
+        <v>0</v>
+      </c>
+      <c r="Q278">
+        <v>2</v>
+      </c>
+      <c r="R278" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>260</v>
+      </c>
+      <c r="B279" t="s">
+        <v>261</v>
+      </c>
+      <c r="C279" t="s">
+        <v>41</v>
+      </c>
+      <c r="D279">
+        <v>1.5</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>4</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>4</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>0</v>
+      </c>
+      <c r="O279">
+        <v>0</v>
+      </c>
+      <c r="P279">
+        <v>0</v>
+      </c>
+      <c r="Q279">
+        <v>3</v>
+      </c>
+      <c r="R279" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>262</v>
+      </c>
+      <c r="R280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>263</v>
+      </c>
+      <c r="B281" t="s">
+        <v>261</v>
+      </c>
+      <c r="C281" t="s">
+        <v>41</v>
+      </c>
+      <c r="D281">
+        <v>1.5</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>4</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>4</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>0</v>
+      </c>
+      <c r="O281">
+        <v>0</v>
+      </c>
+      <c r="P281">
+        <v>0</v>
+      </c>
+      <c r="Q281">
+        <v>1</v>
+      </c>
+      <c r="R281" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>263</v>
+      </c>
+      <c r="B282" t="s">
+        <v>264</v>
+      </c>
+      <c r="C282" t="s">
+        <v>41</v>
+      </c>
+      <c r="D282">
+        <v>3.01</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>2</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>2</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
+      </c>
+      <c r="N282">
+        <v>0</v>
+      </c>
+      <c r="O282">
+        <v>0</v>
+      </c>
+      <c r="P282">
+        <v>0</v>
+      </c>
+      <c r="Q282">
+        <v>2</v>
+      </c>
+      <c r="R282" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>263</v>
+      </c>
+      <c r="B283" t="s">
+        <v>213</v>
+      </c>
+      <c r="C283" t="s">
+        <v>38</v>
+      </c>
+      <c r="D283">
+        <v>2.99</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>150</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>0</v>
+      </c>
+      <c r="O283">
+        <v>0</v>
+      </c>
+      <c r="P283">
+        <v>0</v>
+      </c>
+      <c r="Q283">
+        <v>3</v>
+      </c>
+      <c r="R283" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>263</v>
+      </c>
+      <c r="B284" t="s">
+        <v>202</v>
+      </c>
+      <c r="C284" t="s">
+        <v>38</v>
+      </c>
+      <c r="D284">
+        <v>2.99</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>150</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+      <c r="M284">
+        <v>0</v>
+      </c>
+      <c r="N284">
+        <v>0</v>
+      </c>
+      <c r="O284">
+        <v>0</v>
+      </c>
+      <c r="P284">
+        <v>0</v>
+      </c>
+      <c r="Q284">
+        <v>3</v>
+      </c>
+      <c r="R284" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>265</v>
+      </c>
+      <c r="B285" t="s">
+        <v>264</v>
+      </c>
+      <c r="C285" t="s">
+        <v>41</v>
+      </c>
+      <c r="D285">
+        <v>3.01</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>4</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>4</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
+      </c>
+      <c r="N285">
+        <v>0</v>
+      </c>
+      <c r="O285">
+        <v>0</v>
+      </c>
+      <c r="P285">
+        <v>0</v>
+      </c>
+      <c r="Q285">
+        <v>4</v>
+      </c>
+      <c r="R285" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>265</v>
+      </c>
+      <c r="B286" t="s">
+        <v>272</v>
+      </c>
+      <c r="C286" t="s">
+        <v>41</v>
+      </c>
+      <c r="D286">
+        <v>3.04</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>6</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>6</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>0</v>
+      </c>
+      <c r="O286">
+        <v>0</v>
+      </c>
+      <c r="P286">
+        <v>0</v>
+      </c>
+      <c r="Q286">
+        <v>3</v>
+      </c>
+      <c r="R286" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>266</v>
+      </c>
+      <c r="B287" t="s">
+        <v>273</v>
+      </c>
+      <c r="C287" t="s">
+        <v>145</v>
+      </c>
+      <c r="D287">
+        <v>6.67</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>20</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>0</v>
+      </c>
+      <c r="O287">
+        <v>0</v>
+      </c>
+      <c r="P287">
+        <v>0</v>
+      </c>
+      <c r="Q287">
+        <v>7</v>
+      </c>
+      <c r="R287" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>266</v>
+      </c>
+      <c r="B288" t="s">
+        <v>197</v>
+      </c>
+      <c r="C288" t="s">
+        <v>41</v>
+      </c>
+      <c r="D288">
+        <v>0.82</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>2</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>2</v>
+      </c>
+      <c r="L288">
+        <v>0</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>0</v>
+      </c>
+      <c r="O288">
+        <v>0</v>
+      </c>
+      <c r="P288">
+        <v>0</v>
+      </c>
+      <c r="Q288">
+        <v>2</v>
+      </c>
+      <c r="R288" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>267</v>
+      </c>
+      <c r="B289" t="s">
+        <v>22</v>
+      </c>
+      <c r="C289" t="s">
+        <v>38</v>
+      </c>
+      <c r="D289">
+        <v>2.69</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>6</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>6</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>0</v>
+      </c>
+      <c r="O289">
+        <v>0</v>
+      </c>
+      <c r="P289">
+        <v>0</v>
+      </c>
+      <c r="Q289">
+        <v>4</v>
+      </c>
+      <c r="R289" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>268</v>
+      </c>
+      <c r="R290" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>269</v>
+      </c>
+      <c r="R291" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>270</v>
+      </c>
+      <c r="R292" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>271</v>
+      </c>
+      <c r="B293" t="s">
+        <v>90</v>
+      </c>
+      <c r="C293" t="s">
+        <v>38</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>150</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>0</v>
+      </c>
+      <c r="L293">
+        <v>0</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>0</v>
+      </c>
+      <c r="O293">
+        <v>0</v>
+      </c>
+      <c r="P293">
+        <v>0</v>
+      </c>
+      <c r="Q293">
+        <v>4</v>
+      </c>
+      <c r="R293" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>271</v>
+      </c>
+      <c r="B294" t="s">
+        <v>91</v>
+      </c>
+      <c r="C294" t="s">
+        <v>38</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>150</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>0</v>
+      </c>
+      <c r="L294">
+        <v>0</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
+      </c>
+      <c r="N294">
+        <v>0</v>
+      </c>
+      <c r="O294">
+        <v>0</v>
+      </c>
+      <c r="P294">
+        <v>0</v>
+      </c>
+      <c r="Q294">
+        <v>3</v>
+      </c>
+      <c r="R294" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>271</v>
+      </c>
+      <c r="B295" t="s">
+        <v>283</v>
+      </c>
+      <c r="C295" t="s">
+        <v>38</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>150</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
+        <v>0</v>
+      </c>
+      <c r="O295">
+        <v>0</v>
+      </c>
+      <c r="P295">
+        <v>0</v>
+      </c>
+      <c r="Q295">
+        <v>3</v>
+      </c>
+      <c r="R295" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>274</v>
+      </c>
+      <c r="B296" t="s">
+        <v>257</v>
+      </c>
+      <c r="C296" t="s">
+        <v>38</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>150</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
+      </c>
+      <c r="N296">
+        <v>0</v>
+      </c>
+      <c r="O296">
+        <v>0</v>
+      </c>
+      <c r="P296">
+        <v>0</v>
+      </c>
+      <c r="Q296">
+        <v>4</v>
+      </c>
+      <c r="R296" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>275</v>
+      </c>
+      <c r="R297" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>276</v>
+      </c>
+      <c r="R298" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>277</v>
+      </c>
+      <c r="B299" t="s">
+        <v>151</v>
+      </c>
+      <c r="C299" t="s">
+        <v>20</v>
+      </c>
+      <c r="D299">
+        <v>2.81</v>
+      </c>
+      <c r="E299">
+        <v>6</v>
+      </c>
+      <c r="F299">
+        <v>6</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>0</v>
+      </c>
+      <c r="O299">
+        <v>0</v>
+      </c>
+      <c r="P299">
+        <v>0</v>
+      </c>
+      <c r="Q299">
+        <v>4</v>
+      </c>
+      <c r="R299" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>277</v>
+      </c>
+      <c r="B300" t="s">
+        <v>161</v>
+      </c>
+      <c r="C300" t="s">
+        <v>20</v>
+      </c>
+      <c r="D300">
+        <v>2.81</v>
+      </c>
+      <c r="E300">
+        <v>6</v>
+      </c>
+      <c r="F300">
+        <v>6</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
+      </c>
+      <c r="N300">
+        <v>0</v>
+      </c>
+      <c r="O300">
+        <v>0</v>
+      </c>
+      <c r="P300">
+        <v>0</v>
+      </c>
+      <c r="Q300">
+        <v>4</v>
+      </c>
+      <c r="R300" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>277</v>
+      </c>
+      <c r="B301" t="s">
+        <v>162</v>
+      </c>
+      <c r="C301" t="s">
+        <v>20</v>
+      </c>
+      <c r="D301">
+        <v>2.8</v>
+      </c>
+      <c r="E301">
+        <v>6</v>
+      </c>
+      <c r="F301">
+        <v>6</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>0</v>
+      </c>
+      <c r="M301">
+        <v>0</v>
+      </c>
+      <c r="N301">
+        <v>0</v>
+      </c>
+      <c r="O301">
+        <v>0</v>
+      </c>
+      <c r="P301">
+        <v>0</v>
+      </c>
+      <c r="Q301">
+        <v>3</v>
+      </c>
+      <c r="R301" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>277</v>
+      </c>
+      <c r="B302" t="s">
+        <v>284</v>
+      </c>
+      <c r="C302" t="s">
+        <v>20</v>
+      </c>
+      <c r="D302">
+        <v>3.1</v>
+      </c>
+      <c r="E302">
+        <v>6</v>
+      </c>
+      <c r="F302">
+        <v>6</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
+      </c>
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302">
+        <v>0</v>
+      </c>
+      <c r="P302">
+        <v>0</v>
+      </c>
+      <c r="Q302">
+        <v>4</v>
+      </c>
+      <c r="R302" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>277</v>
+      </c>
+      <c r="B303" t="s">
+        <v>285</v>
+      </c>
+      <c r="C303" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303">
+        <v>3.12</v>
+      </c>
+      <c r="E303">
+        <v>6</v>
+      </c>
+      <c r="F303">
+        <v>6</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+      <c r="M303">
+        <v>0</v>
+      </c>
+      <c r="N303">
+        <v>0</v>
+      </c>
+      <c r="O303">
+        <v>0</v>
+      </c>
+      <c r="P303">
+        <v>0</v>
+      </c>
+      <c r="Q303">
+        <v>3</v>
+      </c>
+      <c r="R303" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>278</v>
+      </c>
+      <c r="B304" t="s">
+        <v>175</v>
+      </c>
+      <c r="C304" t="s">
+        <v>38</v>
+      </c>
+      <c r="D304">
+        <v>3.06</v>
+      </c>
+      <c r="E304">
+        <v>6</v>
+      </c>
+      <c r="F304">
+        <v>6</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>0</v>
+      </c>
+      <c r="O304">
+        <v>0</v>
+      </c>
+      <c r="P304">
+        <v>0</v>
+      </c>
+      <c r="Q304">
+        <v>4</v>
+      </c>
+      <c r="R304" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>278</v>
+      </c>
+      <c r="B305" t="s">
+        <v>286</v>
+      </c>
+      <c r="C305" t="s">
+        <v>38</v>
+      </c>
+      <c r="D305">
+        <v>3.13</v>
+      </c>
+      <c r="E305">
+        <v>6</v>
+      </c>
+      <c r="F305">
+        <v>6</v>
+      </c>
+      <c r="G305">
+        <v>0</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
+      <c r="L305">
+        <v>0</v>
+      </c>
+      <c r="M305">
+        <v>0</v>
+      </c>
+      <c r="N305">
+        <v>0</v>
+      </c>
+      <c r="O305">
+        <v>0</v>
+      </c>
+      <c r="P305">
+        <v>0</v>
+      </c>
+      <c r="Q305">
+        <v>3</v>
+      </c>
+      <c r="R305" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>278</v>
+      </c>
+      <c r="B306" t="s">
+        <v>287</v>
+      </c>
+      <c r="C306" t="s">
+        <v>38</v>
+      </c>
+      <c r="D306">
+        <v>3.09</v>
+      </c>
+      <c r="E306">
+        <v>6</v>
+      </c>
+      <c r="F306">
+        <v>6</v>
+      </c>
+      <c r="G306">
+        <v>0</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306">
+        <v>0</v>
+      </c>
+      <c r="N306">
+        <v>0</v>
+      </c>
+      <c r="O306">
+        <v>0</v>
+      </c>
+      <c r="P306">
+        <v>0</v>
+      </c>
+      <c r="Q306">
+        <v>3</v>
+      </c>
+      <c r="R306" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>278</v>
+      </c>
+      <c r="B307" t="s">
+        <v>288</v>
+      </c>
+      <c r="C307" t="s">
+        <v>229</v>
+      </c>
+      <c r="D307">
+        <v>5</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>15</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
+        <v>7</v>
+      </c>
+      <c r="R307" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>279</v>
+      </c>
+      <c r="B308" t="s">
+        <v>289</v>
+      </c>
+      <c r="C308" t="s">
+        <v>38</v>
+      </c>
+      <c r="D308">
+        <v>3.1</v>
+      </c>
+      <c r="E308">
+        <v>6</v>
+      </c>
+      <c r="F308">
+        <v>6</v>
+      </c>
+      <c r="G308">
+        <v>6</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308">
+        <v>0</v>
+      </c>
+      <c r="P308">
+        <v>0</v>
+      </c>
+      <c r="Q308">
+        <v>4</v>
+      </c>
+      <c r="R308" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>279</v>
+      </c>
+      <c r="B309" t="s">
+        <v>290</v>
+      </c>
+      <c r="C309" t="s">
+        <v>38</v>
+      </c>
+      <c r="D309">
+        <v>3.09</v>
+      </c>
+      <c r="E309">
+        <v>6</v>
+      </c>
+      <c r="F309">
+        <v>6</v>
+      </c>
+      <c r="G309">
+        <v>6</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
+      </c>
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309">
+        <v>0</v>
+      </c>
+      <c r="P309">
+        <v>0</v>
+      </c>
+      <c r="Q309">
+        <v>3</v>
+      </c>
+      <c r="R309" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>279</v>
+      </c>
+      <c r="B310" t="s">
+        <v>291</v>
+      </c>
+      <c r="C310" t="s">
+        <v>38</v>
+      </c>
+      <c r="D310">
+        <v>3.09</v>
+      </c>
+      <c r="E310">
+        <v>6</v>
+      </c>
+      <c r="F310">
+        <v>6</v>
+      </c>
+      <c r="G310">
+        <v>6</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+      <c r="M310">
+        <v>0</v>
+      </c>
+      <c r="N310">
+        <v>0</v>
+      </c>
+      <c r="O310">
+        <v>0</v>
+      </c>
+      <c r="P310">
+        <v>0</v>
+      </c>
+      <c r="Q310">
+        <v>3</v>
+      </c>
+      <c r="R310" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>280</v>
+      </c>
+      <c r="B311" t="s">
+        <v>257</v>
+      </c>
+      <c r="C311" t="s">
+        <v>38</v>
+      </c>
+      <c r="D311">
+        <v>2.08</v>
+      </c>
+      <c r="E311">
+        <v>4</v>
+      </c>
+      <c r="F311">
+        <v>4</v>
+      </c>
+      <c r="G311">
+        <v>4</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>0</v>
+      </c>
+      <c r="L311">
+        <v>0</v>
+      </c>
+      <c r="M311">
+        <v>0</v>
+      </c>
+      <c r="N311">
+        <v>0</v>
+      </c>
+      <c r="O311">
+        <v>0</v>
+      </c>
+      <c r="P311">
+        <v>0</v>
+      </c>
+      <c r="Q311">
+        <v>4</v>
+      </c>
+      <c r="R311" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>280</v>
+      </c>
+      <c r="B312" t="s">
+        <v>283</v>
+      </c>
+      <c r="C312" t="s">
+        <v>38</v>
+      </c>
+      <c r="D312">
+        <v>3.02</v>
+      </c>
+      <c r="E312">
+        <v>6</v>
+      </c>
+      <c r="F312">
+        <v>6</v>
+      </c>
+      <c r="G312">
+        <v>6</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>0</v>
+      </c>
+      <c r="M312">
+        <v>0</v>
+      </c>
+      <c r="N312">
+        <v>0</v>
+      </c>
+      <c r="O312">
+        <v>0</v>
+      </c>
+      <c r="P312">
+        <v>0</v>
+      </c>
+      <c r="Q312">
+        <v>4</v>
+      </c>
+      <c r="R312" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>281</v>
+      </c>
+      <c r="R313" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>282</v>
+      </c>
+      <c r="R314" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>292</v>
+      </c>
+      <c r="B315" t="s">
+        <v>293</v>
+      </c>
+      <c r="C315" t="s">
+        <v>38</v>
+      </c>
+      <c r="D315">
+        <v>3.09</v>
+      </c>
+      <c r="E315">
+        <v>6</v>
+      </c>
+      <c r="F315">
+        <v>6</v>
+      </c>
+      <c r="G315">
+        <v>6</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+      <c r="M315">
+        <v>0</v>
+      </c>
+      <c r="N315">
+        <v>0</v>
+      </c>
+      <c r="O315">
+        <v>0</v>
+      </c>
+      <c r="P315">
+        <v>0</v>
+      </c>
+      <c r="Q315">
+        <v>4</v>
+      </c>
+      <c r="R315" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>292</v>
+      </c>
+      <c r="B316" t="s">
+        <v>294</v>
+      </c>
+      <c r="C316" t="s">
+        <v>38</v>
+      </c>
+      <c r="D316">
+        <v>2.9</v>
+      </c>
+      <c r="E316">
+        <v>6</v>
+      </c>
+      <c r="F316">
+        <v>6</v>
+      </c>
+      <c r="G316">
+        <v>6</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+      <c r="M316">
+        <v>0</v>
+      </c>
+      <c r="N316">
+        <v>0</v>
+      </c>
+      <c r="O316">
+        <v>0</v>
+      </c>
+      <c r="P316">
+        <v>0</v>
+      </c>
+      <c r="Q316">
+        <v>4</v>
+      </c>
+      <c r="R316" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>292</v>
+      </c>
+      <c r="B317" t="s">
+        <v>295</v>
+      </c>
+      <c r="C317" t="s">
+        <v>20</v>
+      </c>
+      <c r="D317">
+        <v>3.14</v>
+      </c>
+      <c r="E317">
+        <v>6</v>
+      </c>
+      <c r="F317">
+        <v>6</v>
+      </c>
+      <c r="G317">
+        <v>0</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <v>0</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
+      </c>
+      <c r="N317">
+        <v>0</v>
+      </c>
+      <c r="O317">
+        <v>0</v>
+      </c>
+      <c r="P317">
+        <v>0</v>
+      </c>
+      <c r="Q317">
+        <v>3</v>
+      </c>
+      <c r="R317" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>296</v>
+      </c>
+      <c r="B318" t="s">
+        <v>90</v>
+      </c>
+      <c r="C318" t="s">
+        <v>38</v>
+      </c>
+      <c r="D318">
+        <v>3.02</v>
+      </c>
+      <c r="E318">
+        <v>6</v>
+      </c>
+      <c r="F318">
+        <v>6</v>
+      </c>
+      <c r="G318">
+        <v>6</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318">
+        <v>0</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>0</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>0</v>
+      </c>
+      <c r="O318">
+        <v>0</v>
+      </c>
+      <c r="P318">
+        <v>0</v>
+      </c>
+      <c r="Q318">
+        <v>4</v>
+      </c>
+      <c r="R318" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>296</v>
+      </c>
+      <c r="B319" t="s">
+        <v>91</v>
+      </c>
+      <c r="C319" t="s">
+        <v>38</v>
+      </c>
+      <c r="D319">
+        <v>3.02</v>
+      </c>
+      <c r="E319">
+        <v>6</v>
+      </c>
+      <c r="F319">
+        <v>6</v>
+      </c>
+      <c r="G319">
+        <v>6</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>0</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>0</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
+      </c>
+      <c r="N319">
+        <v>0</v>
+      </c>
+      <c r="O319">
+        <v>0</v>
+      </c>
+      <c r="P319">
+        <v>0</v>
+      </c>
+      <c r="Q319">
+        <v>3</v>
+      </c>
+      <c r="R319" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>297</v>
+      </c>
+      <c r="R320" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>298</v>
+      </c>
+      <c r="B321" t="s">
+        <v>299</v>
+      </c>
+      <c r="C321" t="s">
+        <v>20</v>
+      </c>
+      <c r="D321">
+        <v>3.14</v>
+      </c>
+      <c r="E321">
+        <v>6</v>
+      </c>
+      <c r="F321">
+        <v>6</v>
+      </c>
+      <c r="G321">
+        <v>6</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>0</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
+      </c>
+      <c r="N321">
+        <v>0</v>
+      </c>
+      <c r="O321">
+        <v>0</v>
+      </c>
+      <c r="P321">
+        <v>0</v>
+      </c>
+      <c r="Q321">
+        <v>4</v>
+      </c>
+      <c r="R321" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>300</v>
+      </c>
+      <c r="R322" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>301</v>
+      </c>
+      <c r="R323" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>57</v>
+      </c>
+      <c r="R324" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>302</v>
+      </c>
+      <c r="B325" t="s">
+        <v>310</v>
+      </c>
+      <c r="C325" t="s">
+        <v>246</v>
+      </c>
+      <c r="D325">
+        <v>4.05</v>
+      </c>
+      <c r="E325">
+        <v>8</v>
+      </c>
+      <c r="F325">
+        <v>8</v>
+      </c>
+      <c r="G325">
+        <v>8</v>
+      </c>
+      <c r="H325">
+        <v>0</v>
+      </c>
+      <c r="I325">
+        <v>0</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+      <c r="M325">
+        <v>0</v>
+      </c>
+      <c r="N325">
+        <v>0</v>
+      </c>
+      <c r="O325">
+        <v>0</v>
+      </c>
+      <c r="P325">
+        <v>0</v>
+      </c>
+      <c r="Q325">
+        <v>5</v>
+      </c>
+      <c r="R325" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>302</v>
+      </c>
+      <c r="B326" t="s">
+        <v>311</v>
+      </c>
+      <c r="C326" t="s">
+        <v>246</v>
+      </c>
+      <c r="D326">
+        <v>3.02</v>
+      </c>
+      <c r="E326">
+        <v>6</v>
+      </c>
+      <c r="F326">
+        <v>6</v>
+      </c>
+      <c r="G326">
+        <v>6</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+      <c r="I326">
+        <v>0</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>0</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
+      </c>
+      <c r="N326">
+        <v>0</v>
+      </c>
+      <c r="O326">
+        <v>0</v>
+      </c>
+      <c r="P326">
+        <v>0</v>
+      </c>
+      <c r="Q326">
+        <v>4</v>
+      </c>
+      <c r="R326" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>302</v>
+      </c>
+      <c r="B327" t="s">
+        <v>312</v>
+      </c>
+      <c r="C327" t="s">
+        <v>246</v>
+      </c>
+      <c r="D327">
+        <v>3.02</v>
+      </c>
+      <c r="E327">
+        <v>6</v>
+      </c>
+      <c r="F327">
+        <v>6</v>
+      </c>
+      <c r="G327">
+        <v>6</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+      <c r="I327">
+        <v>0</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>0</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="N327">
+        <v>0</v>
+      </c>
+      <c r="O327">
+        <v>0</v>
+      </c>
+      <c r="P327">
+        <v>0</v>
+      </c>
+      <c r="Q327">
+        <v>3</v>
+      </c>
+      <c r="R327" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>302</v>
+      </c>
+      <c r="B328" t="s">
+        <v>245</v>
+      </c>
+      <c r="C328" t="s">
+        <v>246</v>
+      </c>
+      <c r="D328">
+        <v>3.03</v>
+      </c>
+      <c r="E328">
+        <v>6</v>
+      </c>
+      <c r="F328">
+        <v>6</v>
+      </c>
+      <c r="G328">
+        <v>6</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
+      </c>
+      <c r="N328">
+        <v>0</v>
+      </c>
+      <c r="O328">
+        <v>0</v>
+      </c>
+      <c r="P328">
+        <v>0</v>
+      </c>
+      <c r="Q328">
+        <v>3</v>
+      </c>
+      <c r="R328" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>302</v>
+      </c>
+      <c r="B329" t="s">
+        <v>249</v>
+      </c>
+      <c r="C329" t="s">
+        <v>246</v>
+      </c>
+      <c r="D329">
+        <v>3.02</v>
+      </c>
+      <c r="E329">
+        <v>6</v>
+      </c>
+      <c r="F329">
+        <v>6</v>
+      </c>
+      <c r="G329">
+        <v>6</v>
+      </c>
+      <c r="H329">
+        <v>0</v>
+      </c>
+      <c r="I329">
+        <v>0</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>0</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="N329">
+        <v>0</v>
+      </c>
+      <c r="O329">
+        <v>0</v>
+      </c>
+      <c r="P329">
+        <v>0</v>
+      </c>
+      <c r="Q329">
+        <v>3</v>
+      </c>
+      <c r="R329" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>302</v>
+      </c>
+      <c r="B330" t="s">
+        <v>254</v>
+      </c>
+      <c r="C330" t="s">
+        <v>246</v>
+      </c>
+      <c r="D330">
+        <v>3.02</v>
+      </c>
+      <c r="E330">
+        <v>6</v>
+      </c>
+      <c r="F330">
+        <v>6</v>
+      </c>
+      <c r="G330">
+        <v>6</v>
+      </c>
+      <c r="H330">
+        <v>0</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>0</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="N330">
+        <v>0</v>
+      </c>
+      <c r="O330">
+        <v>0</v>
+      </c>
+      <c r="P330">
+        <v>0</v>
+      </c>
+      <c r="Q330">
+        <v>3</v>
+      </c>
+      <c r="R330" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>302</v>
+      </c>
+      <c r="B331" t="s">
+        <v>256</v>
+      </c>
+      <c r="C331" t="s">
+        <v>246</v>
+      </c>
+      <c r="D331">
+        <v>3.03</v>
+      </c>
+      <c r="E331">
+        <v>6</v>
+      </c>
+      <c r="F331">
+        <v>6</v>
+      </c>
+      <c r="G331">
+        <v>6</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+      <c r="M331">
+        <v>0</v>
+      </c>
+      <c r="N331">
+        <v>0</v>
+      </c>
+      <c r="O331">
+        <v>0</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>4</v>
+      </c>
+      <c r="R331" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>302</v>
+      </c>
+      <c r="B332" t="s">
+        <v>258</v>
+      </c>
+      <c r="C332" t="s">
+        <v>246</v>
+      </c>
+      <c r="D332">
+        <v>3</v>
+      </c>
+      <c r="E332">
+        <v>6</v>
+      </c>
+      <c r="F332">
+        <v>6</v>
+      </c>
+      <c r="G332">
+        <v>6</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>0</v>
+      </c>
+      <c r="L332">
+        <v>0</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="N332">
+        <v>0</v>
+      </c>
+      <c r="O332">
+        <v>0</v>
+      </c>
+      <c r="P332">
+        <v>0</v>
+      </c>
+      <c r="Q332">
+        <v>3</v>
+      </c>
+      <c r="R332" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>303</v>
+      </c>
+      <c r="R333" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>304</v>
+      </c>
+      <c r="R334" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>305</v>
+      </c>
+      <c r="B335" t="s">
+        <v>313</v>
+      </c>
+      <c r="C335" t="s">
+        <v>20</v>
+      </c>
+      <c r="D335">
+        <v>3.04</v>
+      </c>
+      <c r="E335">
+        <v>6</v>
+      </c>
+      <c r="F335">
+        <v>6</v>
+      </c>
+      <c r="G335">
+        <v>6</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>0</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+      <c r="M335">
+        <v>0</v>
+      </c>
+      <c r="N335">
+        <v>0</v>
+      </c>
+      <c r="O335">
+        <v>0</v>
+      </c>
+      <c r="P335">
+        <v>0</v>
+      </c>
+      <c r="Q335">
+        <v>3</v>
+      </c>
+      <c r="R335" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>305</v>
+      </c>
+      <c r="B336" t="s">
+        <v>314</v>
+      </c>
+      <c r="C336" t="s">
+        <v>20</v>
+      </c>
+      <c r="D336">
+        <v>3.03</v>
+      </c>
+      <c r="E336">
+        <v>3</v>
+      </c>
+      <c r="F336">
+        <v>3</v>
+      </c>
+      <c r="G336">
+        <v>3</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>0</v>
+      </c>
+      <c r="N336">
+        <v>0</v>
+      </c>
+      <c r="O336">
+        <v>0</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>2</v>
+      </c>
+      <c r="R336" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>306</v>
+      </c>
+      <c r="R337" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>307</v>
+      </c>
+      <c r="R338" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>308</v>
+      </c>
+      <c r="B339" t="s">
+        <v>315</v>
+      </c>
+      <c r="C339" t="s">
+        <v>20</v>
+      </c>
+      <c r="D339">
+        <v>3.01</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+      <c r="F339">
+        <v>6</v>
+      </c>
+      <c r="G339">
+        <v>0</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <v>6</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+      <c r="M339">
+        <v>0</v>
+      </c>
+      <c r="N339">
+        <v>0</v>
+      </c>
+      <c r="O339">
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <v>0</v>
+      </c>
+      <c r="Q339">
+        <v>4</v>
+      </c>
+      <c r="R339" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>308</v>
+      </c>
+      <c r="B340" t="s">
+        <v>316</v>
+      </c>
+      <c r="C340" t="s">
+        <v>20</v>
+      </c>
+      <c r="D340">
+        <v>3.02</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>6</v>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>6</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+      <c r="M340">
+        <v>0</v>
+      </c>
+      <c r="N340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <v>3</v>
+      </c>
+      <c r="R340" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>308</v>
+      </c>
+      <c r="B341" t="s">
+        <v>49</v>
+      </c>
+      <c r="C341" t="s">
+        <v>38</v>
+      </c>
+      <c r="D341">
+        <v>3.13</v>
+      </c>
+      <c r="E341">
+        <v>3</v>
+      </c>
+      <c r="F341">
+        <v>3</v>
+      </c>
+      <c r="G341">
+        <v>3</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>2</v>
+      </c>
+      <c r="R341" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>308</v>
+      </c>
+      <c r="B342" t="s">
+        <v>37</v>
+      </c>
+      <c r="C342" t="s">
+        <v>38</v>
+      </c>
+      <c r="D342">
+        <v>4.63</v>
+      </c>
+      <c r="E342">
+        <v>6</v>
+      </c>
+      <c r="F342">
+        <v>6</v>
+      </c>
+      <c r="G342">
+        <v>6</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>0</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+      <c r="M342">
+        <v>0</v>
+      </c>
+      <c r="N342">
+        <v>0</v>
+      </c>
+      <c r="O342">
+        <v>0</v>
+      </c>
+      <c r="P342">
+        <v>0</v>
+      </c>
+      <c r="Q342">
+        <v>3</v>
+      </c>
+      <c r="R342" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>309</v>
+      </c>
+      <c r="B343" t="s">
+        <v>317</v>
+      </c>
+      <c r="C343" t="s">
+        <v>38</v>
+      </c>
+      <c r="D343">
+        <v>3</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>6</v>
+      </c>
+      <c r="G343">
+        <v>0</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>6</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+      <c r="M343">
+        <v>0</v>
+      </c>
+      <c r="N343">
+        <v>0</v>
+      </c>
+      <c r="O343">
+        <v>0</v>
+      </c>
+      <c r="P343">
+        <v>0</v>
+      </c>
+      <c r="Q343">
+        <v>4</v>
+      </c>
+      <c r="R343" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>309</v>
+      </c>
+      <c r="B344" t="s">
+        <v>318</v>
+      </c>
+      <c r="C344" t="s">
+        <v>26</v>
+      </c>
+      <c r="D344">
+        <v>10</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>0</v>
+      </c>
+      <c r="G344">
+        <v>0</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>30</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
+      </c>
+      <c r="N344">
+        <v>0</v>
+      </c>
+      <c r="O344">
+        <v>0</v>
+      </c>
+      <c r="P344">
+        <v>0</v>
+      </c>
+      <c r="Q344">
+        <v>7</v>
+      </c>
+      <c r="R344" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>319</v>
+      </c>
+      <c r="B345" t="s">
+        <v>320</v>
+      </c>
+      <c r="C345" t="s">
+        <v>20</v>
+      </c>
+      <c r="D345">
+        <v>3.03</v>
+      </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
+      <c r="F345">
+        <v>6</v>
+      </c>
+      <c r="G345">
+        <v>0</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345">
+        <v>6</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+      <c r="M345">
+        <v>0</v>
+      </c>
+      <c r="N345">
+        <v>0</v>
+      </c>
+      <c r="O345">
+        <v>0</v>
+      </c>
+      <c r="P345">
+        <v>0</v>
+      </c>
+      <c r="Q345">
+        <v>4</v>
+      </c>
+      <c r="R345" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>321</v>
+      </c>
+      <c r="B346" t="s">
+        <v>328</v>
+      </c>
+      <c r="C346" t="s">
+        <v>20</v>
+      </c>
+      <c r="D346">
+        <v>1.83</v>
+      </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
+      <c r="F346">
+        <v>4</v>
+      </c>
+      <c r="G346">
+        <v>0</v>
+      </c>
+      <c r="H346">
+        <v>0</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>4</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>0</v>
+      </c>
+      <c r="O346">
+        <v>0</v>
+      </c>
+      <c r="P346">
+        <v>0</v>
+      </c>
+      <c r="Q346">
+        <v>2</v>
+      </c>
+      <c r="R346" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>321</v>
+      </c>
+      <c r="B347" t="s">
+        <v>235</v>
+      </c>
+      <c r="C347" t="s">
+        <v>38</v>
+      </c>
+      <c r="D347">
+        <v>0.5</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="F347">
+        <v>1</v>
+      </c>
+      <c r="G347">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>0</v>
+      </c>
+      <c r="I347">
+        <v>0</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>0</v>
+      </c>
+      <c r="L347">
+        <v>0</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
+      </c>
+      <c r="N347">
+        <v>0</v>
+      </c>
+      <c r="O347">
+        <v>0</v>
+      </c>
+      <c r="P347">
+        <v>0</v>
+      </c>
+      <c r="Q347">
+        <v>1</v>
+      </c>
+      <c r="R347" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>321</v>
+      </c>
+      <c r="B348" t="s">
+        <v>196</v>
+      </c>
+      <c r="C348" t="s">
+        <v>38</v>
+      </c>
+      <c r="D348">
+        <v>2.99</v>
+      </c>
+      <c r="E348">
+        <v>6</v>
+      </c>
+      <c r="F348">
+        <v>6</v>
+      </c>
+      <c r="G348">
+        <v>6</v>
+      </c>
+      <c r="H348">
+        <v>0</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>0</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+      <c r="M348">
+        <v>0</v>
+      </c>
+      <c r="N348">
+        <v>0</v>
+      </c>
+      <c r="O348">
+        <v>0</v>
+      </c>
+      <c r="P348">
+        <v>0</v>
+      </c>
+      <c r="Q348">
+        <v>3</v>
+      </c>
+      <c r="R348" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>321</v>
+      </c>
+      <c r="B349" t="s">
+        <v>234</v>
+      </c>
+      <c r="C349" t="s">
+        <v>38</v>
+      </c>
+      <c r="D349">
+        <v>2.99</v>
+      </c>
+      <c r="E349">
+        <v>6</v>
+      </c>
+      <c r="F349">
+        <v>6</v>
+      </c>
+      <c r="G349">
+        <v>6</v>
+      </c>
+      <c r="H349">
+        <v>0</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+      <c r="M349">
+        <v>0</v>
+      </c>
+      <c r="N349">
+        <v>0</v>
+      </c>
+      <c r="O349">
+        <v>0</v>
+      </c>
+      <c r="P349">
+        <v>0</v>
+      </c>
+      <c r="Q349">
+        <v>3</v>
+      </c>
+      <c r="R349" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>322</v>
+      </c>
+      <c r="R350" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>323</v>
+      </c>
+      <c r="B351" t="s">
+        <v>198</v>
+      </c>
+      <c r="C351" t="s">
+        <v>38</v>
+      </c>
+      <c r="D351">
+        <v>2.99</v>
+      </c>
+      <c r="E351">
+        <v>6</v>
+      </c>
+      <c r="F351">
+        <v>6</v>
+      </c>
+      <c r="G351">
+        <v>6</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>0</v>
+      </c>
+      <c r="L351">
+        <v>0</v>
+      </c>
+      <c r="M351">
+        <v>0</v>
+      </c>
+      <c r="N351">
+        <v>0</v>
+      </c>
+      <c r="O351">
+        <v>0</v>
+      </c>
+      <c r="P351">
+        <v>0</v>
+      </c>
+      <c r="Q351">
+        <v>3</v>
+      </c>
+      <c r="R351" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>323</v>
+      </c>
+      <c r="B352" t="s">
+        <v>37</v>
+      </c>
+      <c r="C352" t="s">
+        <v>38</v>
+      </c>
+      <c r="D352">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="E352">
+        <v>5</v>
+      </c>
+      <c r="F352">
+        <v>5</v>
+      </c>
+      <c r="G352">
+        <v>5</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352">
+        <v>0</v>
+      </c>
+      <c r="L352">
+        <v>0</v>
+      </c>
+      <c r="M352">
+        <v>0</v>
+      </c>
+      <c r="N352">
+        <v>0</v>
+      </c>
+      <c r="O352">
+        <v>0</v>
+      </c>
+      <c r="P352">
+        <v>0</v>
+      </c>
+      <c r="Q352">
+        <v>3</v>
+      </c>
+      <c r="R352" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>324</v>
+      </c>
+      <c r="R353" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>325</v>
+      </c>
+      <c r="R354" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>326</v>
+      </c>
+      <c r="R355" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>327</v>
+      </c>
+      <c r="B356" t="s">
+        <v>228</v>
+      </c>
+      <c r="C356" t="s">
+        <v>229</v>
+      </c>
+      <c r="D356">
+        <v>7</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>0</v>
+      </c>
+      <c r="G356">
+        <v>0</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+      <c r="I356">
+        <v>0</v>
+      </c>
+      <c r="J356">
+        <v>21</v>
+      </c>
+      <c r="K356">
+        <v>0</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+      <c r="M356">
+        <v>0</v>
+      </c>
+      <c r="N356">
+        <v>0</v>
+      </c>
+      <c r="O356">
+        <v>0</v>
+      </c>
+      <c r="P356">
+        <v>0</v>
+      </c>
+      <c r="Q356">
+        <v>8</v>
+      </c>
+      <c r="R356" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>329</v>
+      </c>
+      <c r="R357" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>330</v>
+      </c>
+      <c r="R358" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>331</v>
+      </c>
+      <c r="R359" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>332</v>
+      </c>
+      <c r="R360" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>333</v>
+      </c>
+      <c r="R361" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>334</v>
+      </c>
+      <c r="R362" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>335</v>
+      </c>
+      <c r="R363" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>336</v>
+      </c>
+      <c r="R364" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>337</v>
+      </c>
+      <c r="R365" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>338</v>
+      </c>
+      <c r="R366" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>339</v>
+      </c>
+      <c r="R367" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>340</v>
+      </c>
+      <c r="R368" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>341</v>
+      </c>
+      <c r="R369" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>342</v>
+      </c>
+      <c r="B370" t="s">
+        <v>150</v>
+      </c>
+      <c r="C370" t="s">
+        <v>26</v>
+      </c>
+      <c r="D370">
+        <v>5</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>0</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+      <c r="J370">
+        <v>15</v>
+      </c>
+      <c r="K370">
+        <v>0</v>
+      </c>
+      <c r="L370">
+        <v>0</v>
+      </c>
+      <c r="M370">
+        <v>0</v>
+      </c>
+      <c r="N370">
+        <v>0</v>
+      </c>
+      <c r="O370">
+        <v>0</v>
+      </c>
+      <c r="P370">
+        <v>0</v>
+      </c>
+      <c r="Q370">
+        <v>6</v>
+      </c>
+      <c r="R370" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q371">
+        <v>0</v>
+      </c>
+      <c r="R371" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>343</v>
+      </c>
+      <c r="B372" t="s">
+        <v>344</v>
+      </c>
+      <c r="C372" t="s">
+        <v>217</v>
+      </c>
+      <c r="D372">
+        <v>8.67</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>0</v>
+      </c>
+      <c r="G372">
+        <v>0</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>26</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>0</v>
+      </c>
+      <c r="M372">
+        <v>0</v>
+      </c>
+      <c r="N372">
+        <v>0</v>
+      </c>
+      <c r="O372">
+        <v>0</v>
+      </c>
+      <c r="P372">
+        <v>0</v>
+      </c>
+      <c r="Q372">
+        <v>5</v>
+      </c>
+      <c r="R372" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>343</v>
+      </c>
+      <c r="B373" t="s">
+        <v>40</v>
+      </c>
+      <c r="C373" t="s">
+        <v>217</v>
+      </c>
+      <c r="D373">
+        <v>7</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>0</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>21</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373">
+        <v>0</v>
+      </c>
+      <c r="N373">
+        <v>0</v>
+      </c>
+      <c r="O373">
+        <v>0</v>
+      </c>
+      <c r="P373">
+        <v>0</v>
+      </c>
+      <c r="Q373">
+        <v>4</v>
+      </c>
+      <c r="R373" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>345</v>
+      </c>
+      <c r="R374" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>346</v>
+      </c>
+      <c r="R375" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>347</v>
+      </c>
+      <c r="B376" t="s">
+        <v>248</v>
+      </c>
+      <c r="C376" t="s">
+        <v>41</v>
+      </c>
+      <c r="D376">
+        <v>3.03</v>
+      </c>
+      <c r="E376">
+        <v>6</v>
+      </c>
+      <c r="F376">
+        <v>6</v>
+      </c>
+      <c r="G376">
+        <v>6</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>0</v>
+      </c>
+      <c r="L376">
+        <v>0</v>
+      </c>
+      <c r="M376">
+        <v>0</v>
+      </c>
+      <c r="N376">
+        <v>0</v>
+      </c>
+      <c r="O376">
+        <v>0</v>
+      </c>
+      <c r="P376">
+        <v>0</v>
+      </c>
+      <c r="Q376">
+        <v>4</v>
+      </c>
+      <c r="R376" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>347</v>
+      </c>
+      <c r="B377" t="s">
+        <v>264</v>
+      </c>
+      <c r="C377" t="s">
+        <v>41</v>
+      </c>
+      <c r="D377">
+        <v>3.01</v>
+      </c>
+      <c r="E377">
+        <v>6</v>
+      </c>
+      <c r="F377">
+        <v>6</v>
+      </c>
+      <c r="G377">
+        <v>6</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+      <c r="M377">
+        <v>0</v>
+      </c>
+      <c r="N377">
+        <v>0</v>
+      </c>
+      <c r="O377">
+        <v>0</v>
+      </c>
+      <c r="P377">
+        <v>0</v>
+      </c>
+      <c r="Q377">
+        <v>3</v>
+      </c>
+      <c r="R377" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>347</v>
+      </c>
+      <c r="B378" t="s">
+        <v>197</v>
+      </c>
+      <c r="C378" t="s">
+        <v>41</v>
+      </c>
+      <c r="D378">
+        <v>0.82</v>
+      </c>
+      <c r="E378">
+        <v>2</v>
+      </c>
+      <c r="F378">
+        <v>2</v>
+      </c>
+      <c r="G378">
+        <v>2</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+      <c r="M378">
+        <v>0</v>
+      </c>
+      <c r="N378">
+        <v>0</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
+      </c>
+      <c r="P378">
+        <v>0</v>
+      </c>
+      <c r="Q378">
+        <v>3</v>
+      </c>
+      <c r="R378" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>348</v>
+      </c>
+      <c r="B379" t="s">
+        <v>250</v>
+      </c>
+      <c r="C379" t="s">
+        <v>41</v>
+      </c>
+      <c r="D379">
+        <v>3.02</v>
+      </c>
+      <c r="E379">
+        <v>6</v>
+      </c>
+      <c r="F379">
+        <v>6</v>
+      </c>
+      <c r="G379">
+        <v>6</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+      <c r="I379">
+        <v>0</v>
+      </c>
+      <c r="J379">
+        <v>0</v>
+      </c>
+      <c r="K379">
+        <v>0</v>
+      </c>
+      <c r="L379">
+        <v>0</v>
+      </c>
+      <c r="M379">
+        <v>0</v>
+      </c>
+      <c r="N379">
+        <v>0</v>
+      </c>
+      <c r="O379">
+        <v>0</v>
+      </c>
+      <c r="P379">
+        <v>0</v>
+      </c>
+      <c r="Q379">
+        <v>4</v>
+      </c>
+      <c r="R379" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>348</v>
+      </c>
+      <c r="B380" t="s">
+        <v>255</v>
+      </c>
+      <c r="C380" t="s">
+        <v>41</v>
+      </c>
+      <c r="D380">
+        <v>3.02</v>
+      </c>
+      <c r="E380">
+        <v>6</v>
+      </c>
+      <c r="F380">
+        <v>6</v>
+      </c>
+      <c r="G380">
+        <v>6</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>0</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>0</v>
+      </c>
+      <c r="M380">
+        <v>0</v>
+      </c>
+      <c r="N380">
+        <v>0</v>
+      </c>
+      <c r="O380">
+        <v>0</v>
+      </c>
+      <c r="P380">
+        <v>0</v>
+      </c>
+      <c r="Q380">
+        <v>3</v>
+      </c>
+      <c r="R380" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>348</v>
+      </c>
+      <c r="B381" t="s">
+        <v>261</v>
+      </c>
+      <c r="C381" t="s">
+        <v>41</v>
+      </c>
+      <c r="D381">
+        <v>1.51</v>
+      </c>
+      <c r="E381">
+        <v>3</v>
+      </c>
+      <c r="F381">
+        <v>3</v>
+      </c>
+      <c r="G381">
+        <v>3</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>0</v>
+      </c>
+      <c r="K381">
+        <v>0</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+      <c r="M381">
+        <v>0</v>
+      </c>
+      <c r="N381">
+        <v>0</v>
+      </c>
+      <c r="O381">
+        <v>0</v>
+      </c>
+      <c r="P381">
+        <v>0</v>
+      </c>
+      <c r="Q381">
+        <v>2</v>
+      </c>
+      <c r="R381" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>349</v>
+      </c>
+      <c r="B382" t="s">
+        <v>261</v>
+      </c>
+      <c r="C382" t="s">
+        <v>41</v>
+      </c>
+      <c r="D382">
+        <v>1.51</v>
+      </c>
+      <c r="E382">
+        <v>3</v>
+      </c>
+      <c r="F382">
+        <v>3</v>
+      </c>
+      <c r="G382">
+        <v>3</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+      <c r="I382">
+        <v>0</v>
+      </c>
+      <c r="J382">
+        <v>0</v>
+      </c>
+      <c r="K382">
+        <v>0</v>
+      </c>
+      <c r="L382">
+        <v>0</v>
+      </c>
+      <c r="M382">
+        <v>0</v>
+      </c>
+      <c r="N382">
+        <v>0</v>
+      </c>
+      <c r="O382">
+        <v>0</v>
+      </c>
+      <c r="P382">
+        <v>0</v>
+      </c>
+      <c r="Q382">
+        <v>2</v>
+      </c>
+      <c r="R382" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>349</v>
+      </c>
+      <c r="B383" t="s">
+        <v>272</v>
+      </c>
+      <c r="C383" t="s">
+        <v>41</v>
+      </c>
+      <c r="D383">
+        <v>3.04</v>
+      </c>
+      <c r="E383">
+        <v>6</v>
+      </c>
+      <c r="F383">
+        <v>6</v>
+      </c>
+      <c r="G383">
+        <v>6</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+      <c r="I383">
+        <v>0</v>
+      </c>
+      <c r="J383">
+        <v>0</v>
+      </c>
+      <c r="K383">
+        <v>0</v>
+      </c>
+      <c r="L383">
+        <v>0</v>
+      </c>
+      <c r="M383">
+        <v>0</v>
+      </c>
+      <c r="N383">
+        <v>0</v>
+      </c>
+      <c r="O383">
+        <v>0</v>
+      </c>
+      <c r="P383">
+        <v>0</v>
+      </c>
+      <c r="Q383">
+        <v>3</v>
+      </c>
+      <c r="R383" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>350</v>
+      </c>
+      <c r="R384" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>351</v>
+      </c>
+      <c r="B385" t="s">
+        <v>356</v>
+      </c>
+      <c r="C385" t="s">
+        <v>20</v>
+      </c>
+      <c r="D385">
+        <v>3.01</v>
+      </c>
+      <c r="E385">
+        <v>3</v>
+      </c>
+      <c r="F385">
+        <v>3</v>
+      </c>
+      <c r="G385">
+        <v>3</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+      <c r="J385">
+        <v>0</v>
+      </c>
+      <c r="K385">
+        <v>0</v>
+      </c>
+      <c r="L385">
+        <v>0</v>
+      </c>
+      <c r="M385">
+        <v>0</v>
+      </c>
+      <c r="N385">
+        <v>0</v>
+      </c>
+      <c r="O385">
+        <v>0</v>
+      </c>
+      <c r="P385">
+        <v>0</v>
+      </c>
+      <c r="Q385">
+        <v>3</v>
+      </c>
+      <c r="R385" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>351</v>
+      </c>
+      <c r="B386" t="s">
+        <v>357</v>
+      </c>
+      <c r="C386" t="s">
+        <v>20</v>
+      </c>
+      <c r="D386">
+        <v>3.01</v>
+      </c>
+      <c r="E386">
+        <v>6</v>
+      </c>
+      <c r="F386">
+        <v>6</v>
+      </c>
+      <c r="G386">
+        <v>6</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+      <c r="I386">
+        <v>0</v>
+      </c>
+      <c r="J386">
+        <v>0</v>
+      </c>
+      <c r="K386">
+        <v>0</v>
+      </c>
+      <c r="L386">
+        <v>0</v>
+      </c>
+      <c r="M386">
+        <v>0</v>
+      </c>
+      <c r="N386">
+        <v>0</v>
+      </c>
+      <c r="O386">
+        <v>0</v>
+      </c>
+      <c r="P386">
+        <v>0</v>
+      </c>
+      <c r="Q386">
+        <v>3</v>
+      </c>
+      <c r="R386" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>351</v>
+      </c>
+      <c r="B387" t="s">
+        <v>358</v>
+      </c>
+      <c r="C387" t="s">
+        <v>20</v>
+      </c>
+      <c r="D387">
+        <v>1.52</v>
+      </c>
+      <c r="E387">
+        <v>3</v>
+      </c>
+      <c r="F387">
+        <v>3</v>
+      </c>
+      <c r="G387">
+        <v>3</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+      <c r="I387">
+        <v>0</v>
+      </c>
+      <c r="J387">
+        <v>0</v>
+      </c>
+      <c r="K387">
+        <v>0</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
+      <c r="M387">
+        <v>0</v>
+      </c>
+      <c r="N387">
+        <v>0</v>
+      </c>
+      <c r="O387">
+        <v>0</v>
+      </c>
+      <c r="P387">
+        <v>0</v>
+      </c>
+      <c r="Q387">
+        <v>2</v>
+      </c>
+      <c r="R387" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>352</v>
+      </c>
+      <c r="B388" t="s">
+        <v>358</v>
+      </c>
+      <c r="C388" t="s">
+        <v>20</v>
+      </c>
+      <c r="D388">
+        <v>1.52</v>
+      </c>
+      <c r="E388">
+        <v>3</v>
+      </c>
+      <c r="F388">
+        <v>3</v>
+      </c>
+      <c r="G388">
+        <v>3</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+      <c r="I388">
+        <v>0</v>
+      </c>
+      <c r="J388">
+        <v>0</v>
+      </c>
+      <c r="K388">
+        <v>0</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+      <c r="M388">
+        <v>0</v>
+      </c>
+      <c r="N388">
+        <v>0</v>
+      </c>
+      <c r="O388">
+        <v>0</v>
+      </c>
+      <c r="P388">
+        <v>0</v>
+      </c>
+      <c r="Q388">
+        <v>2</v>
+      </c>
+      <c r="R388" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>352</v>
+      </c>
+      <c r="B389" t="s">
+        <v>359</v>
+      </c>
+      <c r="C389" t="s">
+        <v>20</v>
+      </c>
+      <c r="D389">
+        <v>3.03</v>
+      </c>
+      <c r="E389">
+        <v>6</v>
+      </c>
+      <c r="F389">
+        <v>6</v>
+      </c>
+      <c r="G389">
+        <v>6</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+      <c r="I389">
+        <v>0</v>
+      </c>
+      <c r="J389">
+        <v>0</v>
+      </c>
+      <c r="K389">
+        <v>0</v>
+      </c>
+      <c r="L389">
+        <v>0</v>
+      </c>
+      <c r="M389">
+        <v>0</v>
+      </c>
+      <c r="N389">
+        <v>0</v>
+      </c>
+      <c r="O389">
+        <v>0</v>
+      </c>
+      <c r="P389">
+        <v>0</v>
+      </c>
+      <c r="Q389">
+        <v>3</v>
+      </c>
+      <c r="R389" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>352</v>
+      </c>
+      <c r="B390" t="s">
+        <v>314</v>
+      </c>
+      <c r="C390" t="s">
+        <v>20</v>
+      </c>
+      <c r="D390">
+        <v>1</v>
+      </c>
+      <c r="E390">
+        <v>2</v>
+      </c>
+      <c r="F390">
+        <v>2</v>
+      </c>
+      <c r="G390">
+        <v>2</v>
+      </c>
+      <c r="H390">
+        <v>0</v>
+      </c>
+      <c r="I390">
+        <v>0</v>
+      </c>
+      <c r="J390">
+        <v>0</v>
+      </c>
+      <c r="K390">
+        <v>0</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+      <c r="M390">
+        <v>0</v>
+      </c>
+      <c r="N390">
+        <v>0</v>
+      </c>
+      <c r="O390">
+        <v>0</v>
+      </c>
+      <c r="P390">
+        <v>0</v>
+      </c>
+      <c r="Q390">
+        <v>1</v>
+      </c>
+      <c r="R390" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>353</v>
+      </c>
+      <c r="R391" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>354</v>
+      </c>
+      <c r="B392" t="s">
+        <v>313</v>
+      </c>
+      <c r="C392" t="s">
+        <v>20</v>
+      </c>
+      <c r="D392">
+        <v>3.04</v>
+      </c>
+      <c r="E392">
+        <v>6</v>
+      </c>
+      <c r="F392">
+        <v>6</v>
+      </c>
+      <c r="G392">
+        <v>6</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
+      <c r="I392">
+        <v>0</v>
+      </c>
+      <c r="J392">
+        <v>0</v>
+      </c>
+      <c r="K392">
+        <v>0</v>
+      </c>
+      <c r="L392">
+        <v>0</v>
+      </c>
+      <c r="M392">
+        <v>0</v>
+      </c>
+      <c r="N392">
+        <v>0</v>
+      </c>
+      <c r="O392">
+        <v>0</v>
+      </c>
+      <c r="P392">
+        <v>0</v>
+      </c>
+      <c r="Q392">
+        <v>4</v>
+      </c>
+      <c r="R392" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>354</v>
+      </c>
+      <c r="B393" t="s">
+        <v>314</v>
+      </c>
+      <c r="C393" t="s">
+        <v>20</v>
+      </c>
+      <c r="D393">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E393">
+        <v>4</v>
+      </c>
+      <c r="F393">
+        <v>4</v>
+      </c>
+      <c r="G393">
+        <v>4</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
+      </c>
+      <c r="I393">
+        <v>0</v>
+      </c>
+      <c r="J393">
+        <v>0</v>
+      </c>
+      <c r="K393">
+        <v>0</v>
+      </c>
+      <c r="L393">
+        <v>0</v>
+      </c>
+      <c r="M393">
+        <v>0</v>
+      </c>
+      <c r="N393">
+        <v>0</v>
+      </c>
+      <c r="O393">
+        <v>0</v>
+      </c>
+      <c r="P393">
+        <v>0</v>
+      </c>
+      <c r="Q393">
+        <v>3</v>
+      </c>
+      <c r="R393" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>354</v>
+      </c>
+      <c r="B394" t="s">
+        <v>73</v>
+      </c>
+      <c r="C394" t="s">
+        <v>38</v>
+      </c>
+      <c r="D394">
+        <v>3.11</v>
+      </c>
+      <c r="E394">
+        <v>2</v>
+      </c>
+      <c r="F394">
+        <v>2</v>
+      </c>
+      <c r="G394">
+        <v>2</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+      <c r="I394">
+        <v>0</v>
+      </c>
+      <c r="J394">
+        <v>0</v>
+      </c>
+      <c r="K394">
+        <v>0</v>
+      </c>
+      <c r="L394">
+        <v>0</v>
+      </c>
+      <c r="M394">
+        <v>0</v>
+      </c>
+      <c r="N394">
+        <v>0</v>
+      </c>
+      <c r="O394">
+        <v>0</v>
+      </c>
+      <c r="P394">
+        <v>0</v>
+      </c>
+      <c r="Q394">
+        <v>2</v>
+      </c>
+      <c r="R394" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>355</v>
+      </c>
+      <c r="B395" t="s">
+        <v>360</v>
+      </c>
+      <c r="C395" t="s">
+        <v>20</v>
+      </c>
+      <c r="D395">
+        <v>0.34</v>
+      </c>
+      <c r="E395">
+        <v>2</v>
+      </c>
+      <c r="F395">
+        <v>2</v>
+      </c>
+      <c r="G395">
+        <v>2</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
+      </c>
+      <c r="I395">
+        <v>0</v>
+      </c>
+      <c r="J395">
+        <v>0</v>
+      </c>
+      <c r="K395">
+        <v>0</v>
+      </c>
+      <c r="L395">
+        <v>0</v>
+      </c>
+      <c r="M395">
+        <v>0</v>
+      </c>
+      <c r="N395">
+        <v>0</v>
+      </c>
+      <c r="O395">
+        <v>0</v>
+      </c>
+      <c r="P395">
+        <v>0</v>
+      </c>
+      <c r="Q395">
+        <v>2</v>
+      </c>
+      <c r="R395" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>355</v>
+      </c>
+      <c r="B396" t="s">
+        <v>361</v>
+      </c>
+      <c r="C396" t="s">
+        <v>20</v>
+      </c>
+      <c r="D396">
+        <v>3.03</v>
+      </c>
+      <c r="E396">
+        <v>6</v>
+      </c>
+      <c r="F396">
+        <v>6</v>
+      </c>
+      <c r="G396">
+        <v>6</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+      <c r="I396">
+        <v>0</v>
+      </c>
+      <c r="J396">
+        <v>0</v>
+      </c>
+      <c r="K396">
+        <v>0</v>
+      </c>
+      <c r="L396">
+        <v>0</v>
+      </c>
+      <c r="M396">
+        <v>0</v>
+      </c>
+      <c r="N396">
+        <v>0</v>
+      </c>
+      <c r="O396">
+        <v>0</v>
+      </c>
+      <c r="P396">
+        <v>0</v>
+      </c>
+      <c r="Q396">
+        <v>3</v>
+      </c>
+      <c r="R396" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>355</v>
+      </c>
+      <c r="B397" t="s">
+        <v>362</v>
+      </c>
+      <c r="C397" t="s">
+        <v>20</v>
+      </c>
+      <c r="D397">
+        <v>3.01</v>
+      </c>
+      <c r="E397">
+        <v>6</v>
+      </c>
+      <c r="F397">
+        <v>6</v>
+      </c>
+      <c r="G397">
+        <v>6</v>
+      </c>
+      <c r="H397">
+        <v>0</v>
+      </c>
+      <c r="I397">
+        <v>0</v>
+      </c>
+      <c r="J397">
+        <v>0</v>
+      </c>
+      <c r="K397">
+        <v>0</v>
+      </c>
+      <c r="L397">
+        <v>0</v>
+      </c>
+      <c r="M397">
+        <v>0</v>
+      </c>
+      <c r="N397">
+        <v>0</v>
+      </c>
+      <c r="O397">
+        <v>0</v>
+      </c>
+      <c r="P397">
+        <v>0</v>
+      </c>
+      <c r="Q397">
+        <v>4</v>
+      </c>
+      <c r="R397" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>355</v>
+      </c>
+      <c r="B398" t="s">
+        <v>363</v>
+      </c>
+      <c r="C398" t="s">
+        <v>229</v>
+      </c>
+      <c r="D398">
+        <v>5</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+      <c r="F398">
+        <v>0</v>
+      </c>
+      <c r="G398">
+        <v>0</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+      <c r="I398">
+        <v>0</v>
+      </c>
+      <c r="J398">
+        <v>15</v>
+      </c>
+      <c r="K398">
+        <v>0</v>
+      </c>
+      <c r="L398">
+        <v>0</v>
+      </c>
+      <c r="M398">
+        <v>0</v>
+      </c>
+      <c r="N398">
+        <v>0</v>
+      </c>
+      <c r="O398">
+        <v>0</v>
+      </c>
+      <c r="P398">
+        <v>0</v>
+      </c>
+      <c r="Q398">
+        <v>3</v>
+      </c>
+      <c r="R398" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>355</v>
+      </c>
+      <c r="B399" t="s">
+        <v>364</v>
+      </c>
+      <c r="C399" t="s">
+        <v>26</v>
+      </c>
+      <c r="D399">
+        <v>6.33</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+      <c r="F399">
+        <v>0</v>
+      </c>
+      <c r="G399">
+        <v>0</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+      <c r="I399">
+        <v>0</v>
+      </c>
+      <c r="J399">
+        <v>19</v>
+      </c>
+      <c r="K399">
+        <v>0</v>
+      </c>
+      <c r="L399">
+        <v>0</v>
+      </c>
+      <c r="M399">
+        <v>0</v>
+      </c>
+      <c r="N399">
+        <v>0</v>
+      </c>
+      <c r="O399">
+        <v>0</v>
+      </c>
+      <c r="P399">
+        <v>0</v>
+      </c>
+      <c r="Q399">
+        <v>4</v>
+      </c>
+      <c r="R399" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>365</v>
+      </c>
+      <c r="B400" t="s">
+        <v>366</v>
+      </c>
+      <c r="C400" t="s">
+        <v>20</v>
+      </c>
+      <c r="D400">
+        <v>3.04</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+      <c r="F400">
+        <v>0</v>
+      </c>
+      <c r="G400">
+        <v>0</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+      <c r="I400">
+        <v>150</v>
+      </c>
+      <c r="J400">
+        <v>0</v>
+      </c>
+      <c r="K400">
+        <v>0</v>
+      </c>
+      <c r="L400">
+        <v>0</v>
+      </c>
+      <c r="M400">
+        <v>0</v>
+      </c>
+      <c r="N400">
+        <v>0</v>
+      </c>
+      <c r="O400">
+        <v>0</v>
+      </c>
+      <c r="P400">
+        <v>0</v>
+      </c>
+      <c r="Q400">
+        <v>5</v>
+      </c>
+      <c r="R400" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="401" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>365</v>
+      </c>
+      <c r="B401" t="s">
+        <v>238</v>
+      </c>
+      <c r="C401" t="s">
+        <v>217</v>
+      </c>
+      <c r="D401">
+        <v>7</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+      <c r="F401">
+        <v>0</v>
+      </c>
+      <c r="G401">
+        <v>0</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+      <c r="I401">
+        <v>0</v>
+      </c>
+      <c r="J401">
+        <v>21</v>
+      </c>
+      <c r="K401">
+        <v>0</v>
+      </c>
+      <c r="L401">
+        <v>0</v>
+      </c>
+      <c r="M401">
+        <v>0</v>
+      </c>
+      <c r="N401">
+        <v>0</v>
+      </c>
+      <c r="O401">
+        <v>0</v>
+      </c>
+      <c r="P401">
+        <v>0</v>
+      </c>
+      <c r="Q401">
+        <v>7</v>
+      </c>
+      <c r="R401" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="402" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>367</v>
+      </c>
+      <c r="R402" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="403" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>368</v>
+      </c>
+      <c r="B403" t="s">
+        <v>372</v>
+      </c>
+      <c r="C403" t="s">
+        <v>20</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+      <c r="F403">
+        <v>0</v>
+      </c>
+      <c r="G403">
+        <v>0</v>
+      </c>
+      <c r="H403">
+        <v>0</v>
+      </c>
+      <c r="I403">
+        <v>150</v>
+      </c>
+      <c r="J403">
+        <v>0</v>
+      </c>
+      <c r="K403">
+        <v>0</v>
+      </c>
+      <c r="L403">
+        <v>0</v>
+      </c>
+      <c r="M403">
+        <v>0</v>
+      </c>
+      <c r="N403">
+        <v>0</v>
+      </c>
+      <c r="O403">
+        <v>0</v>
+      </c>
+      <c r="P403">
+        <v>0</v>
+      </c>
+      <c r="Q403">
+        <v>4</v>
+      </c>
+      <c r="R403" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="404" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>368</v>
+      </c>
+      <c r="B404" t="s">
+        <v>373</v>
+      </c>
+      <c r="C404" t="s">
+        <v>20</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+      <c r="F404">
+        <v>0</v>
+      </c>
+      <c r="G404">
+        <v>0</v>
+      </c>
+      <c r="H404">
+        <v>0</v>
+      </c>
+      <c r="I404">
+        <v>150</v>
+      </c>
+      <c r="J404">
+        <v>0</v>
+      </c>
+      <c r="K404">
+        <v>0</v>
+      </c>
+      <c r="L404">
+        <v>0</v>
+      </c>
+      <c r="M404">
+        <v>0</v>
+      </c>
+      <c r="N404">
+        <v>0</v>
+      </c>
+      <c r="O404">
+        <v>0</v>
+      </c>
+      <c r="P404">
+        <v>0</v>
+      </c>
+      <c r="Q404">
+        <v>4</v>
+      </c>
+      <c r="R404" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="405" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>368</v>
+      </c>
+      <c r="B405" t="s">
+        <v>374</v>
+      </c>
+      <c r="C405" t="s">
+        <v>20</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <v>0</v>
+      </c>
+      <c r="G405">
+        <v>0</v>
+      </c>
+      <c r="H405">
+        <v>0</v>
+      </c>
+      <c r="I405">
+        <v>150</v>
+      </c>
+      <c r="J405">
+        <v>0</v>
+      </c>
+      <c r="K405">
+        <v>0</v>
+      </c>
+      <c r="L405">
+        <v>0</v>
+      </c>
+      <c r="M405">
+        <v>0</v>
+      </c>
+      <c r="N405">
+        <v>0</v>
+      </c>
+      <c r="O405">
+        <v>0</v>
+      </c>
+      <c r="P405">
+        <v>0</v>
+      </c>
+      <c r="Q405">
+        <v>3</v>
+      </c>
+      <c r="R405" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="406" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>368</v>
+      </c>
+      <c r="B406" t="s">
+        <v>375</v>
+      </c>
+      <c r="C406" t="s">
+        <v>20</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+      <c r="F406">
+        <v>0</v>
+      </c>
+      <c r="G406">
+        <v>0</v>
+      </c>
+      <c r="H406">
+        <v>0</v>
+      </c>
+      <c r="I406">
+        <v>150</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406">
+        <v>0</v>
+      </c>
+      <c r="L406">
+        <v>0</v>
+      </c>
+      <c r="M406">
+        <v>0</v>
+      </c>
+      <c r="N406">
+        <v>0</v>
+      </c>
+      <c r="O406">
+        <v>0</v>
+      </c>
+      <c r="P406">
+        <v>0</v>
+      </c>
+      <c r="Q406">
+        <v>4</v>
+      </c>
+      <c r="R406" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="407" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>369</v>
+      </c>
+      <c r="B407" t="s">
+        <v>376</v>
+      </c>
+      <c r="C407" t="s">
+        <v>217</v>
+      </c>
+      <c r="D407">
+        <v>2.67</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+      <c r="F407">
+        <v>0</v>
+      </c>
+      <c r="G407">
+        <v>0</v>
+      </c>
+      <c r="H407">
+        <v>0</v>
+      </c>
+      <c r="I407">
+        <v>0</v>
+      </c>
+      <c r="J407">
+        <v>8</v>
+      </c>
+      <c r="K407">
+        <v>0</v>
+      </c>
+      <c r="L407">
+        <v>0</v>
+      </c>
+      <c r="M407">
+        <v>0</v>
+      </c>
+      <c r="N407">
+        <v>0</v>
+      </c>
+      <c r="O407">
+        <v>0</v>
+      </c>
+      <c r="P407">
+        <v>0</v>
+      </c>
+      <c r="Q407">
+        <v>3</v>
+      </c>
+      <c r="R407" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="408" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>370</v>
+      </c>
+      <c r="R408" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="409" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>371</v>
+      </c>
+      <c r="R409" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="410" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>371</v>
+      </c>
+      <c r="R410" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="411" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>371</v>
+      </c>
+      <c r="R411" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="412" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>371</v>
+      </c>
+      <c r="R412" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="413" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R413" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="414" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R414" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="415" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R415" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="416" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R416" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="417" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R417" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="418" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R418" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="419" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R419" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="420" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R420" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="421" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R421" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="422" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R422" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R423" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="424" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R424" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R425" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="426" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R426" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="427" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R427" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="428" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R428" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="429" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R429" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="430" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R430" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="431" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R431" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="432" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R432" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="433" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R433" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="434" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R434" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="435" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R435" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="436" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R436" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="437" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R437" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="438" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R438" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="439" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R439" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="440" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R440" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="441" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R441" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="442" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R442" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="443" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R443" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="444" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R444" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="445" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R445" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="446" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R446" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="447" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R447" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="448" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R448" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="449" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R449" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="450" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R450" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="451" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R451" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="452" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R452" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="453" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R453" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="454" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R454" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="455" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R455" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="456" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>59</v>
+      </c>
+      <c r="B456" t="s">
+        <v>51</v>
+      </c>
+      <c r="C456" t="s">
+        <v>60</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+      <c r="R456" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="457" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
         <v>61</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B457" t="s">
         <v>51</v>
       </c>
-      <c r="C269" t="s">
+      <c r="C457" t="s">
         <v>52</v>
       </c>
-      <c r="D269" t="s">
+      <c r="D457" t="s">
         <v>62</v>
       </c>
-      <c r="E269" t="s">
+      <c r="E457" t="s">
         <v>62</v>
       </c>
-      <c r="F269" t="s">
+      <c r="F457" t="s">
         <v>62</v>
       </c>
-      <c r="G269" t="s">
+      <c r="G457" t="s">
         <v>62</v>
       </c>
-      <c r="H269" t="s">
+      <c r="H457" t="s">
         <v>62</v>
       </c>
-      <c r="Q269" t="s">
+      <c r="Q457" t="s">
         <v>62</v>
       </c>
-      <c r="R269" t="s">
+      <c r="R457" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data/herbicide_records.xlsx
+++ b/data/herbicide_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="396">
   <si>
     <t>Date</t>
   </si>
@@ -1150,6 +1150,63 @@
   </si>
   <si>
     <t>DG39001</t>
+  </si>
+  <si>
+    <t>DG24000</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>LF08008</t>
+  </si>
+  <si>
+    <t>LP06013</t>
+  </si>
+  <si>
+    <t>LF08009</t>
+  </si>
+  <si>
+    <t>LF08032</t>
+  </si>
+  <si>
+    <t>LF05008</t>
+  </si>
+  <si>
+    <t>LP05012</t>
+  </si>
+  <si>
+    <t>LF08017</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>DG23000</t>
+  </si>
+  <si>
+    <t>DG34000</t>
+  </si>
+  <si>
+    <t>DG35000</t>
+  </si>
+  <si>
+    <t>DG19001</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
   </si>
 </sst>
 </file>
@@ -20067,6 +20124,54 @@
       <c r="A409" t="s">
         <v>371</v>
       </c>
+      <c r="B409" t="s">
+        <v>360</v>
+      </c>
+      <c r="C409" t="s">
+        <v>20</v>
+      </c>
+      <c r="D409">
+        <v>0.34</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+      <c r="F409">
+        <v>0</v>
+      </c>
+      <c r="G409">
+        <v>0</v>
+      </c>
+      <c r="H409">
+        <v>0</v>
+      </c>
+      <c r="I409">
+        <v>50</v>
+      </c>
+      <c r="J409">
+        <v>0</v>
+      </c>
+      <c r="K409">
+        <v>0</v>
+      </c>
+      <c r="L409">
+        <v>0</v>
+      </c>
+      <c r="M409">
+        <v>0</v>
+      </c>
+      <c r="N409">
+        <v>0</v>
+      </c>
+      <c r="O409">
+        <v>0</v>
+      </c>
+      <c r="P409">
+        <v>0</v>
+      </c>
+      <c r="Q409">
+        <v>2</v>
+      </c>
       <c r="R409" t="s">
         <v>21</v>
       </c>
@@ -20075,6 +20180,54 @@
       <c r="A410" t="s">
         <v>371</v>
       </c>
+      <c r="B410" t="s">
+        <v>361</v>
+      </c>
+      <c r="C410" t="s">
+        <v>20</v>
+      </c>
+      <c r="D410">
+        <v>3.03</v>
+      </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
+      <c r="F410">
+        <v>0</v>
+      </c>
+      <c r="G410">
+        <v>0</v>
+      </c>
+      <c r="H410">
+        <v>0</v>
+      </c>
+      <c r="I410">
+        <v>150</v>
+      </c>
+      <c r="J410">
+        <v>0</v>
+      </c>
+      <c r="K410">
+        <v>0</v>
+      </c>
+      <c r="L410">
+        <v>0</v>
+      </c>
+      <c r="M410">
+        <v>0</v>
+      </c>
+      <c r="N410">
+        <v>0</v>
+      </c>
+      <c r="O410">
+        <v>0</v>
+      </c>
+      <c r="P410">
+        <v>0</v>
+      </c>
+      <c r="Q410">
+        <v>4</v>
+      </c>
       <c r="R410" t="s">
         <v>21</v>
       </c>
@@ -20083,6 +20236,54 @@
       <c r="A411" t="s">
         <v>371</v>
       </c>
+      <c r="B411" t="s">
+        <v>362</v>
+      </c>
+      <c r="C411" t="s">
+        <v>20</v>
+      </c>
+      <c r="D411">
+        <v>3.01</v>
+      </c>
+      <c r="E411">
+        <v>0</v>
+      </c>
+      <c r="F411">
+        <v>0</v>
+      </c>
+      <c r="G411">
+        <v>0</v>
+      </c>
+      <c r="H411">
+        <v>0</v>
+      </c>
+      <c r="I411">
+        <v>150</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+      <c r="K411">
+        <v>0</v>
+      </c>
+      <c r="L411">
+        <v>0</v>
+      </c>
+      <c r="M411">
+        <v>0</v>
+      </c>
+      <c r="N411">
+        <v>0</v>
+      </c>
+      <c r="O411">
+        <v>0</v>
+      </c>
+      <c r="P411">
+        <v>0</v>
+      </c>
+      <c r="Q411">
+        <v>3</v>
+      </c>
       <c r="R411" t="s">
         <v>21</v>
       </c>
@@ -20091,106 +20292,976 @@
       <c r="A412" t="s">
         <v>371</v>
       </c>
+      <c r="B412" t="s">
+        <v>377</v>
+      </c>
+      <c r="C412" t="s">
+        <v>217</v>
+      </c>
+      <c r="D412">
+        <v>8</v>
+      </c>
+      <c r="E412">
+        <v>0</v>
+      </c>
+      <c r="F412">
+        <v>0</v>
+      </c>
+      <c r="G412">
+        <v>0</v>
+      </c>
+      <c r="H412">
+        <v>0</v>
+      </c>
+      <c r="J412">
+        <v>24</v>
+      </c>
+      <c r="K412">
+        <v>0</v>
+      </c>
+      <c r="L412">
+        <v>0</v>
+      </c>
+      <c r="M412">
+        <v>0</v>
+      </c>
+      <c r="N412">
+        <v>0</v>
+      </c>
+      <c r="O412">
+        <v>0</v>
+      </c>
+      <c r="P412">
+        <v>0</v>
+      </c>
+      <c r="Q412">
+        <v>8</v>
+      </c>
       <c r="R412" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="413" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>378</v>
+      </c>
+      <c r="B413" t="s">
+        <v>379</v>
+      </c>
+      <c r="C413" t="s">
+        <v>41</v>
+      </c>
+      <c r="D413">
+        <v>1.02</v>
+      </c>
+      <c r="E413">
+        <v>3</v>
+      </c>
+      <c r="F413">
+        <v>0</v>
+      </c>
+      <c r="G413">
+        <v>3</v>
+      </c>
+      <c r="H413">
+        <v>0</v>
+      </c>
+      <c r="I413">
+        <v>0</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+      <c r="K413">
+        <v>0</v>
+      </c>
+      <c r="L413">
+        <v>0</v>
+      </c>
+      <c r="M413">
+        <v>0</v>
+      </c>
+      <c r="N413">
+        <v>0</v>
+      </c>
+      <c r="O413">
+        <v>0</v>
+      </c>
+      <c r="P413">
+        <v>0</v>
+      </c>
+      <c r="Q413">
+        <v>1</v>
+      </c>
       <c r="R413" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="414" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>378</v>
+      </c>
+      <c r="B414" t="s">
+        <v>380</v>
+      </c>
+      <c r="C414" t="s">
+        <v>20</v>
+      </c>
+      <c r="D414">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="E414">
+        <v>8</v>
+      </c>
+      <c r="F414">
+        <v>0</v>
+      </c>
+      <c r="G414">
+        <v>8</v>
+      </c>
+      <c r="H414">
+        <v>0</v>
+      </c>
+      <c r="I414">
+        <v>0</v>
+      </c>
+      <c r="J414">
+        <v>0</v>
+      </c>
+      <c r="K414">
+        <v>0</v>
+      </c>
+      <c r="L414">
+        <v>0</v>
+      </c>
+      <c r="M414">
+        <v>0</v>
+      </c>
+      <c r="N414">
+        <v>0</v>
+      </c>
+      <c r="O414">
+        <v>0</v>
+      </c>
+      <c r="P414">
+        <v>0</v>
+      </c>
+      <c r="Q414">
+        <v>2</v>
+      </c>
       <c r="R414" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="415" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>378</v>
+      </c>
+      <c r="B415" t="s">
+        <v>381</v>
+      </c>
+      <c r="C415" t="s">
+        <v>41</v>
+      </c>
+      <c r="D415">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E415">
+        <v>6</v>
+      </c>
+      <c r="F415">
+        <v>0</v>
+      </c>
+      <c r="G415">
+        <v>6</v>
+      </c>
+      <c r="H415">
+        <v>0</v>
+      </c>
+      <c r="I415">
+        <v>0</v>
+      </c>
+      <c r="J415">
+        <v>0</v>
+      </c>
+      <c r="K415">
+        <v>0</v>
+      </c>
+      <c r="L415">
+        <v>0</v>
+      </c>
+      <c r="M415">
+        <v>0</v>
+      </c>
+      <c r="N415">
+        <v>0</v>
+      </c>
+      <c r="O415">
+        <v>0</v>
+      </c>
+      <c r="P415">
+        <v>0</v>
+      </c>
+      <c r="Q415">
+        <v>2</v>
+      </c>
       <c r="R415" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="416" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>378</v>
+      </c>
+      <c r="B416" t="s">
+        <v>382</v>
+      </c>
+      <c r="C416" t="s">
+        <v>41</v>
+      </c>
+      <c r="D416">
+        <v>1.03</v>
+      </c>
+      <c r="E416">
+        <v>3</v>
+      </c>
+      <c r="F416">
+        <v>0</v>
+      </c>
+      <c r="G416">
+        <v>3</v>
+      </c>
+      <c r="H416">
+        <v>0</v>
+      </c>
+      <c r="I416">
+        <v>0</v>
+      </c>
+      <c r="J416">
+        <v>0</v>
+      </c>
+      <c r="K416">
+        <v>0</v>
+      </c>
+      <c r="L416">
+        <v>0</v>
+      </c>
+      <c r="M416">
+        <v>0</v>
+      </c>
+      <c r="N416">
+        <v>0</v>
+      </c>
+      <c r="O416">
+        <v>0</v>
+      </c>
+      <c r="P416">
+        <v>0</v>
+      </c>
+      <c r="Q416">
+        <v>1</v>
+      </c>
       <c r="R416" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>378</v>
+      </c>
+      <c r="B417" t="s">
+        <v>383</v>
+      </c>
+      <c r="C417" t="s">
+        <v>41</v>
+      </c>
+      <c r="D417">
+        <v>1.34</v>
+      </c>
+      <c r="E417">
+        <v>5</v>
+      </c>
+      <c r="F417">
+        <v>0</v>
+      </c>
+      <c r="G417">
+        <v>5</v>
+      </c>
+      <c r="H417">
+        <v>0</v>
+      </c>
+      <c r="I417">
+        <v>0</v>
+      </c>
+      <c r="J417">
+        <v>0</v>
+      </c>
+      <c r="K417">
+        <v>0</v>
+      </c>
+      <c r="L417">
+        <v>0</v>
+      </c>
+      <c r="M417">
+        <v>0</v>
+      </c>
+      <c r="N417">
+        <v>0</v>
+      </c>
+      <c r="O417">
+        <v>0</v>
+      </c>
+      <c r="P417">
+        <v>0</v>
+      </c>
+      <c r="Q417">
+        <v>2</v>
+      </c>
       <c r="R417" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="418" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>378</v>
+      </c>
+      <c r="B418" t="s">
+        <v>384</v>
+      </c>
+      <c r="C418" t="s">
+        <v>41</v>
+      </c>
+      <c r="D418">
+        <v>2.67</v>
+      </c>
+      <c r="E418">
+        <v>3</v>
+      </c>
+      <c r="F418">
+        <v>0</v>
+      </c>
+      <c r="G418">
+        <v>3</v>
+      </c>
+      <c r="H418">
+        <v>0</v>
+      </c>
+      <c r="I418">
+        <v>0</v>
+      </c>
+      <c r="J418">
+        <v>0</v>
+      </c>
+      <c r="K418">
+        <v>0</v>
+      </c>
+      <c r="L418">
+        <v>0</v>
+      </c>
+      <c r="M418">
+        <v>0</v>
+      </c>
+      <c r="N418">
+        <v>0</v>
+      </c>
+      <c r="O418">
+        <v>0</v>
+      </c>
+      <c r="P418">
+        <v>0</v>
+      </c>
+      <c r="Q418">
+        <v>1</v>
+      </c>
       <c r="R418" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>378</v>
+      </c>
+      <c r="B419" t="s">
+        <v>385</v>
+      </c>
+      <c r="C419" t="s">
+        <v>41</v>
+      </c>
+      <c r="D419">
+        <v>1</v>
+      </c>
+      <c r="E419">
+        <v>3</v>
+      </c>
+      <c r="F419">
+        <v>0</v>
+      </c>
+      <c r="G419">
+        <v>3</v>
+      </c>
+      <c r="H419">
+        <v>0</v>
+      </c>
+      <c r="I419">
+        <v>0</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+      <c r="K419">
+        <v>0</v>
+      </c>
+      <c r="L419">
+        <v>0</v>
+      </c>
+      <c r="M419">
+        <v>0</v>
+      </c>
+      <c r="N419">
+        <v>0</v>
+      </c>
+      <c r="O419">
+        <v>0</v>
+      </c>
+      <c r="P419">
+        <v>0</v>
+      </c>
+      <c r="Q419">
+        <v>1</v>
+      </c>
       <c r="R419" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>386</v>
+      </c>
+      <c r="B420" t="s">
+        <v>389</v>
+      </c>
+      <c r="C420" t="s">
+        <v>217</v>
+      </c>
+      <c r="D420">
+        <v>8.5</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+      <c r="F420">
+        <v>0</v>
+      </c>
+      <c r="G420">
+        <v>0</v>
+      </c>
+      <c r="H420">
+        <v>0</v>
+      </c>
+      <c r="I420">
+        <v>0</v>
+      </c>
+      <c r="J420">
+        <v>25.5</v>
+      </c>
+      <c r="K420">
+        <v>0</v>
+      </c>
+      <c r="L420">
+        <v>0</v>
+      </c>
+      <c r="M420">
+        <v>0</v>
+      </c>
+      <c r="N420">
+        <v>0</v>
+      </c>
+      <c r="O420">
+        <v>0</v>
+      </c>
+      <c r="P420">
+        <v>0</v>
+      </c>
+      <c r="Q420">
+        <v>4</v>
+      </c>
       <c r="R420" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>386</v>
+      </c>
+      <c r="B421" t="s">
+        <v>390</v>
+      </c>
+      <c r="C421" t="s">
+        <v>217</v>
+      </c>
+      <c r="D421">
+        <v>8</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+      <c r="F421">
+        <v>0</v>
+      </c>
+      <c r="G421">
+        <v>0</v>
+      </c>
+      <c r="H421">
+        <v>0</v>
+      </c>
+      <c r="I421">
+        <v>0</v>
+      </c>
+      <c r="J421">
+        <v>24</v>
+      </c>
+      <c r="K421">
+        <v>0</v>
+      </c>
+      <c r="L421">
+        <v>0</v>
+      </c>
+      <c r="M421">
+        <v>0</v>
+      </c>
+      <c r="N421">
+        <v>0</v>
+      </c>
+      <c r="O421">
+        <v>0</v>
+      </c>
+      <c r="P421">
+        <v>0</v>
+      </c>
+      <c r="Q421">
+        <v>3</v>
+      </c>
       <c r="R421" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="422" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>386</v>
+      </c>
+      <c r="B422" t="s">
+        <v>391</v>
+      </c>
+      <c r="C422" t="s">
+        <v>217</v>
+      </c>
+      <c r="D422">
+        <v>4</v>
+      </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
+      <c r="F422">
+        <v>0</v>
+      </c>
+      <c r="G422">
+        <v>0</v>
+      </c>
+      <c r="H422">
+        <v>0</v>
+      </c>
+      <c r="I422">
+        <v>0</v>
+      </c>
+      <c r="J422">
+        <v>12</v>
+      </c>
+      <c r="K422">
+        <v>0</v>
+      </c>
+      <c r="L422">
+        <v>0</v>
+      </c>
+      <c r="M422">
+        <v>0</v>
+      </c>
+      <c r="N422">
+        <v>0</v>
+      </c>
+      <c r="O422">
+        <v>0</v>
+      </c>
+      <c r="P422">
+        <v>0</v>
+      </c>
+      <c r="Q422">
+        <v>3</v>
+      </c>
       <c r="R422" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>387</v>
+      </c>
+      <c r="B423" t="s">
+        <v>143</v>
+      </c>
+      <c r="C423" t="s">
+        <v>217</v>
+      </c>
+      <c r="D423">
+        <v>4</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+      <c r="F423">
+        <v>0</v>
+      </c>
+      <c r="G423">
+        <v>0</v>
+      </c>
+      <c r="H423">
+        <v>0</v>
+      </c>
+      <c r="I423">
+        <v>0</v>
+      </c>
+      <c r="J423">
+        <v>12</v>
+      </c>
+      <c r="K423">
+        <v>0</v>
+      </c>
+      <c r="L423">
+        <v>0</v>
+      </c>
+      <c r="M423">
+        <v>0</v>
+      </c>
+      <c r="N423">
+        <v>0</v>
+      </c>
+      <c r="O423">
+        <v>0</v>
+      </c>
+      <c r="P423">
+        <v>0</v>
+      </c>
+      <c r="Q423">
+        <v>3</v>
+      </c>
       <c r="R423" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="424" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>387</v>
+      </c>
+      <c r="B424" t="s">
+        <v>273</v>
+      </c>
+      <c r="C424" t="s">
+        <v>217</v>
+      </c>
+      <c r="D424">
+        <v>8</v>
+      </c>
+      <c r="E424">
+        <v>0</v>
+      </c>
+      <c r="F424">
+        <v>0</v>
+      </c>
+      <c r="G424">
+        <v>0</v>
+      </c>
+      <c r="H424">
+        <v>0</v>
+      </c>
+      <c r="I424">
+        <v>0</v>
+      </c>
+      <c r="J424">
+        <v>24</v>
+      </c>
+      <c r="K424">
+        <v>0</v>
+      </c>
+      <c r="L424">
+        <v>0</v>
+      </c>
+      <c r="M424">
+        <v>0</v>
+      </c>
+      <c r="N424">
+        <v>0</v>
+      </c>
+      <c r="O424">
+        <v>0</v>
+      </c>
+      <c r="P424">
+        <v>0</v>
+      </c>
+      <c r="Q424">
+        <v>4</v>
+      </c>
       <c r="R424" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>387</v>
+      </c>
+      <c r="B425" t="s">
+        <v>392</v>
+      </c>
+      <c r="C425" t="s">
+        <v>20</v>
+      </c>
+      <c r="D425">
+        <v>3</v>
+      </c>
+      <c r="E425">
+        <v>0</v>
+      </c>
+      <c r="F425">
+        <v>6</v>
+      </c>
+      <c r="G425">
+        <v>6</v>
+      </c>
+      <c r="H425">
+        <v>0</v>
+      </c>
+      <c r="I425">
+        <v>0</v>
+      </c>
+      <c r="J425">
+        <v>0</v>
+      </c>
+      <c r="K425">
+        <v>0</v>
+      </c>
+      <c r="L425">
+        <v>0</v>
+      </c>
+      <c r="M425">
+        <v>0</v>
+      </c>
+      <c r="N425">
+        <v>0</v>
+      </c>
+      <c r="O425">
+        <v>0</v>
+      </c>
+      <c r="P425">
+        <v>0</v>
+      </c>
+      <c r="Q425">
+        <v>3</v>
+      </c>
       <c r="R425" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="426" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>387</v>
+      </c>
+      <c r="B426" t="s">
+        <v>315</v>
+      </c>
+      <c r="C426" t="s">
+        <v>20</v>
+      </c>
+      <c r="D426">
+        <v>3.01</v>
+      </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
+      <c r="F426">
+        <v>6</v>
+      </c>
+      <c r="G426">
+        <v>6</v>
+      </c>
+      <c r="H426">
+        <v>0</v>
+      </c>
+      <c r="I426">
+        <v>0</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+      <c r="K426">
+        <v>0</v>
+      </c>
+      <c r="L426">
+        <v>0</v>
+      </c>
+      <c r="M426">
+        <v>0</v>
+      </c>
+      <c r="N426">
+        <v>0</v>
+      </c>
+      <c r="O426">
+        <v>0</v>
+      </c>
+      <c r="P426">
+        <v>0</v>
+      </c>
+      <c r="Q426">
+        <v>3</v>
+      </c>
       <c r="R426" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="427" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>388</v>
+      </c>
+      <c r="B427" t="s">
+        <v>316</v>
+      </c>
+      <c r="C427" t="s">
+        <v>20</v>
+      </c>
+      <c r="D427">
+        <v>3.02</v>
+      </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
+      <c r="F427">
+        <v>6</v>
+      </c>
+      <c r="G427">
+        <v>6</v>
+      </c>
+      <c r="H427">
+        <v>0</v>
+      </c>
+      <c r="I427">
+        <v>0</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
+      <c r="K427">
+        <v>0</v>
+      </c>
+      <c r="L427">
+        <v>0</v>
+      </c>
+      <c r="M427">
+        <v>0</v>
+      </c>
+      <c r="N427">
+        <v>0</v>
+      </c>
+      <c r="O427">
+        <v>0</v>
+      </c>
+      <c r="P427">
+        <v>0</v>
+      </c>
+      <c r="Q427">
+        <v>5</v>
+      </c>
       <c r="R427" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>388</v>
+      </c>
+      <c r="B428" t="s">
+        <v>317</v>
+      </c>
+      <c r="C428" t="s">
+        <v>20</v>
+      </c>
+      <c r="D428">
+        <v>3</v>
+      </c>
+      <c r="E428">
+        <v>0</v>
+      </c>
+      <c r="F428">
+        <v>9</v>
+      </c>
+      <c r="G428">
+        <v>9</v>
+      </c>
+      <c r="H428">
+        <v>0</v>
+      </c>
+      <c r="I428">
+        <v>0</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
+      <c r="K428">
+        <v>0</v>
+      </c>
+      <c r="L428">
+        <v>0</v>
+      </c>
+      <c r="M428">
+        <v>0</v>
+      </c>
+      <c r="N428">
+        <v>0</v>
+      </c>
+      <c r="O428">
+        <v>0</v>
+      </c>
+      <c r="P428">
+        <v>0</v>
+      </c>
+      <c r="Q428">
+        <v>4</v>
+      </c>
       <c r="R428" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>393</v>
+      </c>
       <c r="R429" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>394</v>
+      </c>
       <c r="R430" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>395</v>
+      </c>
       <c r="R431" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.25">
       <c r="R432" t="s">
         <v>21</v>
       </c>
